--- a/py/output/hasil_clustering_mahasiswa_AI.xlsx
+++ b/py/output/hasil_clustering_mahasiswa_AI.xlsx
@@ -1,17 +1,17 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Data_Mahasiswa_Lengkap" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Statistik_Klaster" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Distribusi_Klaster" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="PCA_Components" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="Evaluasi_Metrik_K" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Data_Mahasiswa_Lengkap" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Statistik_Klaster" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Distribusi_Klaster" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PCA_Components" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Evaluasi_Metrik_K" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -21,16 +21,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -41,7 +38,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="6">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -49,49 +46,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin"/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -461,147 +421,147 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>Timestamp</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>Jurusan/Fakultas</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>Semester</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>Jenis Kelamin</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>Frekuensi_AI</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>Jenis AI yang paling sering digunakan:</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>AI_Referensi</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>AI_Kerangka</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>AI_Grammar</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>Kualitas_Tugas</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>Efisiensi</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>Ketergantungan</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>Reduksi_Pemahaman</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>Waktu_Tanpa_AI</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>Waktu_Dengan_AI</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>Nilai_Sebelum_AI</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>Nilai_Setelah_AI</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>Apa tantangan terbesar saat menggunakan AI untuk tugas akademik?</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="T1" t="inlineStr">
         <is>
           <t>Saran Anda untuk penggunaan AI yang lebih bertanggung jawab:</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="U1" t="inlineStr">
         <is>
           <t>Cluster</t>
         </is>
       </c>
-      <c r="V1" s="1" t="inlineStr">
+      <c r="V1" t="inlineStr">
         <is>
           <t>Label_Cluster</t>
         </is>
       </c>
-      <c r="W1" s="1" t="inlineStr">
+      <c r="W1" t="inlineStr">
         <is>
           <t>Label_Cluster_Short</t>
         </is>
       </c>
-      <c r="X1" s="1" t="inlineStr">
+      <c r="X1" t="inlineStr">
         <is>
           <t>Jarak_Cluster_0</t>
         </is>
       </c>
-      <c r="Y1" s="1" t="inlineStr">
+      <c r="Y1" t="inlineStr">
         <is>
           <t>Jarak_Cluster_1</t>
         </is>
       </c>
-      <c r="Z1" s="1" t="inlineStr">
+      <c r="Z1" t="inlineStr">
         <is>
           <t>Jarak_Cluster_2</t>
         </is>
       </c>
-      <c r="AA1" s="1" t="inlineStr">
+      <c r="AA1" t="inlineStr">
         <is>
           <t>PCA1</t>
         </is>
       </c>
-      <c r="AB1" s="1" t="inlineStr">
+      <c r="AB1" t="inlineStr">
         <is>
           <t>PCA2</t>
         </is>
       </c>
-      <c r="AC1" s="1" t="inlineStr">
+      <c r="AC1" t="inlineStr">
         <is>
           <t>PCA3</t>
         </is>
@@ -705,13 +665,13 @@
         <v>3.6712</v>
       </c>
       <c r="AA2" t="n">
-        <v>-3.499156246927804</v>
+        <v>-3.499156246927799</v>
       </c>
       <c r="AB2" t="n">
         <v>-1.499938876474217</v>
       </c>
       <c r="AC2" t="n">
-        <v>0.1421875443194814</v>
+        <v>0.1421875443194855</v>
       </c>
     </row>
     <row r="3">
@@ -812,13 +772,13 @@
         <v>8.5626</v>
       </c>
       <c r="AA3" t="n">
-        <v>-4.88393547728326</v>
+        <v>-4.883935477283254</v>
       </c>
       <c r="AB3" t="n">
-        <v>-4.881718483028698</v>
+        <v>-4.881718483028699</v>
       </c>
       <c r="AC3" t="n">
-        <v>1.209684986924336</v>
+        <v>1.209684986924355</v>
       </c>
     </row>
     <row r="4">
@@ -919,13 +879,13 @@
         <v>5.4898</v>
       </c>
       <c r="AA4" t="n">
-        <v>-1.415460547278536</v>
+        <v>-1.415460547278535</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.009248793335534449</v>
+        <v>0.009248793335530065</v>
       </c>
       <c r="AC4" t="n">
-        <v>-3.328569889296963</v>
+        <v>-3.328569889296966</v>
       </c>
     </row>
     <row r="5">
@@ -1026,13 +986,13 @@
         <v>3.4977</v>
       </c>
       <c r="AA5" t="n">
-        <v>-1.481271743328443</v>
+        <v>-1.481271743328442</v>
       </c>
       <c r="AB5" t="n">
-        <v>-0.1373891320491085</v>
+        <v>-0.1373891320491075</v>
       </c>
       <c r="AC5" t="n">
-        <v>-0.0005609207773591605</v>
+        <v>-0.0005609207773616514</v>
       </c>
     </row>
     <row r="6">
@@ -1133,13 +1093,13 @@
         <v>4.2395</v>
       </c>
       <c r="AA6" t="n">
-        <v>-1.580542260294042</v>
+        <v>-1.580542260294039</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.306173764997539</v>
+        <v>1.306173764997538</v>
       </c>
       <c r="AC6" t="n">
-        <v>-0.6557704269898309</v>
+        <v>-0.6557704269898335</v>
       </c>
     </row>
     <row r="7">
@@ -1240,13 +1200,13 @@
         <v>3.8125</v>
       </c>
       <c r="AA7" t="n">
-        <v>-2.908314455220369</v>
+        <v>-2.908314455220365</v>
       </c>
       <c r="AB7" t="n">
-        <v>0.4894135058071589</v>
+        <v>0.4894135058071603</v>
       </c>
       <c r="AC7" t="n">
-        <v>1.142898752696106</v>
+        <v>1.142898752696104</v>
       </c>
     </row>
     <row r="8">
@@ -1347,13 +1307,13 @@
         <v>3.8441</v>
       </c>
       <c r="AA8" t="n">
-        <v>-2.718106725163788</v>
+        <v>-2.718106725163787</v>
       </c>
       <c r="AB8" t="n">
-        <v>-0.5176345918246467</v>
+        <v>-0.5176345918246468</v>
       </c>
       <c r="AC8" t="n">
-        <v>1.132450470681366</v>
+        <v>1.132450470681373</v>
       </c>
     </row>
     <row r="9">
@@ -1454,13 +1414,13 @@
         <v>4.199</v>
       </c>
       <c r="AA9" t="n">
-        <v>-1.925560214182487</v>
+        <v>-1.92556021418249</v>
       </c>
       <c r="AB9" t="n">
-        <v>2.007159976948592</v>
+        <v>2.007159976948588</v>
       </c>
       <c r="AC9" t="n">
-        <v>-2.19511951101439</v>
+        <v>-2.195119511014396</v>
       </c>
     </row>
     <row r="10">
@@ -1567,7 +1527,7 @@
         <v>1.257249119975077</v>
       </c>
       <c r="AC10" t="n">
-        <v>-0.6901152018859004</v>
+        <v>-0.6901152018859029</v>
       </c>
     </row>
     <row r="11">
@@ -1668,13 +1628,13 @@
         <v>2.2759</v>
       </c>
       <c r="AA11" t="n">
-        <v>-0.7437200075425795</v>
+        <v>-0.7437200075425791</v>
       </c>
       <c r="AB11" t="n">
-        <v>-0.5361766494538018</v>
+        <v>-0.5361766494538026</v>
       </c>
       <c r="AC11" t="n">
-        <v>-1.107409137216485</v>
+        <v>-1.107409137216486</v>
       </c>
     </row>
     <row r="12">
@@ -1744,13 +1704,13 @@
       </c>
       <c r="S12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kurangnya pemahaman mendalam
+          <t xml:space="preserve">Kurangnya pemahaman mendalam
 AI bisa bantu menjawab soal atau merangkum teks, tapi kalau hanya disalin tanpa dipahami, </t>
         </is>
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>Gunakan sebagai alat bantu, bukan pengganti
+          <t>Gunakan sebagai alat bantu, bukan pengganti
 AI sebaiknya digunakan untuk membantu memahami konsep</t>
         </is>
       </c>
@@ -1777,13 +1737,13 @@
         <v>4.2498</v>
       </c>
       <c r="AA12" t="n">
-        <v>-2.310265440823518</v>
+        <v>-2.310265440823516</v>
       </c>
       <c r="AB12" t="n">
-        <v>-0.2184184351624283</v>
+        <v>-0.2184184351624266</v>
       </c>
       <c r="AC12" t="n">
-        <v>1.161811674941477</v>
+        <v>1.16181167494148</v>
       </c>
     </row>
     <row r="13">
@@ -1887,10 +1847,10 @@
         <v>-1.105675656302142</v>
       </c>
       <c r="AB13" t="n">
-        <v>2.302174731467933</v>
+        <v>2.302174731467932</v>
       </c>
       <c r="AC13" t="n">
-        <v>0.427212732500648</v>
+        <v>0.4272127325006423</v>
       </c>
     </row>
     <row r="14">
@@ -1991,13 +1951,13 @@
         <v>2.6931</v>
       </c>
       <c r="AA14" t="n">
-        <v>-2.091002840208811</v>
+        <v>-2.091002840208812</v>
       </c>
       <c r="AB14" t="n">
-        <v>-0.7327807760622708</v>
+        <v>-0.7327807760622729</v>
       </c>
       <c r="AC14" t="n">
-        <v>-0.8838770998219004</v>
+        <v>-0.883877099821899</v>
       </c>
     </row>
     <row r="15">
@@ -2067,7 +2027,7 @@
       </c>
       <c r="S15" t="inlineStr">
         <is>
-          <t>Pastinya tidak bisa menelan langsung informasi yang diberikan oleh AI, apalagi terkait pengolahan data dan tatacaranya.
+          <t>Pastinya tidak bisa menelan langsung informasi yang diberikan oleh AI, apalagi terkait pengolahan data dan tatacaranya.
 Perlu ditinjau ulang terkait informasi yang diberikan oleh AI karena tidak sepenuhnya benar</t>
         </is>
       </c>
@@ -2099,13 +2059,13 @@
         <v>3.2178</v>
       </c>
       <c r="AA15" t="n">
-        <v>-2.451495468945263</v>
+        <v>-2.451495468945261</v>
       </c>
       <c r="AB15" t="n">
-        <v>0.8208260375430855</v>
+        <v>0.8208260375430844</v>
       </c>
       <c r="AC15" t="n">
-        <v>-0.190341861354126</v>
+        <v>-0.1903418613541294</v>
       </c>
     </row>
     <row r="16">
@@ -2206,13 +2166,13 @@
         <v>5.5942</v>
       </c>
       <c r="AA16" t="n">
-        <v>0.3569005234151307</v>
+        <v>0.3569005234151267</v>
       </c>
       <c r="AB16" t="n">
-        <v>2.660932701908826</v>
+        <v>2.660932701908822</v>
       </c>
       <c r="AC16" t="n">
-        <v>-2.54505061990223</v>
+        <v>-2.545050619902238</v>
       </c>
     </row>
     <row r="17">
@@ -2313,13 +2273,13 @@
         <v>3.6887</v>
       </c>
       <c r="AA17" t="n">
-        <v>0.5888341544693148</v>
+        <v>0.5888341544693165</v>
       </c>
       <c r="AB17" t="n">
         <v>-1.757265689659792</v>
       </c>
       <c r="AC17" t="n">
-        <v>-0.7923843521645874</v>
+        <v>-0.7923843521645839</v>
       </c>
     </row>
     <row r="18">
@@ -2420,13 +2380,13 @@
         <v>2.932</v>
       </c>
       <c r="AA18" t="n">
-        <v>-2.478049117176598</v>
+        <v>-2.478049117176599</v>
       </c>
       <c r="AB18" t="n">
         <v>1.219986941962116</v>
       </c>
       <c r="AC18" t="n">
-        <v>0.3976709034441137</v>
+        <v>0.3976709034441118</v>
       </c>
     </row>
     <row r="19">
@@ -2527,13 +2487,13 @@
         <v>5.0472</v>
       </c>
       <c r="AA19" t="n">
-        <v>-2.092994828091209</v>
+        <v>-2.092994828091211</v>
       </c>
       <c r="AB19" t="n">
-        <v>-1.17985159087333</v>
+        <v>-1.179851590873334</v>
       </c>
       <c r="AC19" t="n">
-        <v>0.7068152775219297</v>
+        <v>0.7068152775219386</v>
       </c>
     </row>
     <row r="20">
@@ -2634,13 +2594,13 @@
         <v>3.7659</v>
       </c>
       <c r="AA20" t="n">
-        <v>-2.159883113962419</v>
+        <v>-2.15988311396242</v>
       </c>
       <c r="AB20" t="n">
         <v>1.09475886643693</v>
       </c>
       <c r="AC20" t="n">
-        <v>-0.1684256409276667</v>
+        <v>-0.1684256409276681</v>
       </c>
     </row>
     <row r="21">
@@ -2744,10 +2704,10 @@
         <v>-2.068982866269891</v>
       </c>
       <c r="AB21" t="n">
-        <v>0.2489342877196116</v>
+        <v>0.2489342877196098</v>
       </c>
       <c r="AC21" t="n">
-        <v>-0.2125549159928523</v>
+        <v>-0.2125549159928522</v>
       </c>
     </row>
     <row r="22">
@@ -2851,10 +2811,10 @@
         <v>-2.05034391380351</v>
       </c>
       <c r="AB22" t="n">
-        <v>-1.371320936654499</v>
+        <v>-1.371320936654498</v>
       </c>
       <c r="AC22" t="n">
-        <v>1.589330287069618</v>
+        <v>1.589330287069628</v>
       </c>
     </row>
     <row r="23">
@@ -2958,10 +2918,10 @@
         <v>-2.331688539979799</v>
       </c>
       <c r="AB23" t="n">
-        <v>-2.932372525450186</v>
+        <v>-2.932372525450187</v>
       </c>
       <c r="AC23" t="n">
-        <v>0.7661029406955437</v>
+        <v>0.7661029406955576</v>
       </c>
     </row>
     <row r="24">
@@ -3065,10 +3025,10 @@
         <v>-2.606002450931066</v>
       </c>
       <c r="AB24" t="n">
-        <v>2.603290285810227</v>
+        <v>2.603290285810224</v>
       </c>
       <c r="AC24" t="n">
-        <v>-0.9083753522730539</v>
+        <v>-0.9083753522730613</v>
       </c>
     </row>
     <row r="25">
@@ -3169,13 +3129,13 @@
         <v>5.7689</v>
       </c>
       <c r="AA25" t="n">
-        <v>-3.242937059208842</v>
+        <v>-3.24293705920884</v>
       </c>
       <c r="AB25" t="n">
-        <v>-3.607723264684452</v>
+        <v>-3.607723264684454</v>
       </c>
       <c r="AC25" t="n">
-        <v>0.700338537509076</v>
+        <v>0.7003385375090893</v>
       </c>
     </row>
     <row r="26">
@@ -3276,13 +3236,13 @@
         <v>2.9183</v>
       </c>
       <c r="AA26" t="n">
-        <v>-1.743113141665189</v>
+        <v>-1.743113141665188</v>
       </c>
       <c r="AB26" t="n">
-        <v>0.7169807588820338</v>
+        <v>0.7169807588820335</v>
       </c>
       <c r="AC26" t="n">
-        <v>0.8483453515717914</v>
+        <v>0.8483453515717904</v>
       </c>
     </row>
     <row r="27">
@@ -3383,13 +3343,13 @@
         <v>3.0024</v>
       </c>
       <c r="AA27" t="n">
-        <v>-2.840012796652442</v>
+        <v>-2.840012796652441</v>
       </c>
       <c r="AB27" t="n">
-        <v>-0.4490076657002306</v>
+        <v>-0.449007665700231</v>
       </c>
       <c r="AC27" t="n">
-        <v>1.042121295403105</v>
+        <v>1.042121295403107</v>
       </c>
     </row>
     <row r="28">
@@ -3490,13 +3450,13 @@
         <v>4.2647</v>
       </c>
       <c r="AA28" t="n">
-        <v>-1.627503603028988</v>
+        <v>-1.62750360302899</v>
       </c>
       <c r="AB28" t="n">
-        <v>2.142583520047531</v>
+        <v>2.142583520047529</v>
       </c>
       <c r="AC28" t="n">
-        <v>-1.674969250488942</v>
+        <v>-1.674969250488948</v>
       </c>
     </row>
     <row r="29">
@@ -3597,13 +3557,13 @@
         <v>3.8461</v>
       </c>
       <c r="AA29" t="n">
-        <v>-1.494003734044548</v>
+        <v>-1.494003734044549</v>
       </c>
       <c r="AB29" t="n">
-        <v>-0.9757516337408615</v>
+        <v>-0.9757516337408605</v>
       </c>
       <c r="AC29" t="n">
-        <v>0.3761490659025887</v>
+        <v>0.3761490659025932</v>
       </c>
     </row>
     <row r="30">
@@ -3704,13 +3664,13 @@
         <v>2.6028</v>
       </c>
       <c r="AA30" t="n">
-        <v>-1.551590503689831</v>
+        <v>-1.551590503689832</v>
       </c>
       <c r="AB30" t="n">
-        <v>0.4557753201009558</v>
+        <v>0.4557753201009541</v>
       </c>
       <c r="AC30" t="n">
-        <v>-0.2137477407680753</v>
+        <v>-0.2137477407680742</v>
       </c>
     </row>
     <row r="31">
@@ -3811,13 +3771,13 @@
         <v>4.2442</v>
       </c>
       <c r="AA31" t="n">
-        <v>-2.944867143906345</v>
+        <v>-2.944867143906342</v>
       </c>
       <c r="AB31" t="n">
         <v>-2.151932764379195</v>
       </c>
       <c r="AC31" t="n">
-        <v>1.072135462526055</v>
+        <v>1.072135462526062</v>
       </c>
     </row>
     <row r="32">
@@ -3918,13 +3878,13 @@
         <v>3.5976</v>
       </c>
       <c r="AA32" t="n">
-        <v>-2.724820475052029</v>
+        <v>-2.724820475052027</v>
       </c>
       <c r="AB32" t="n">
-        <v>-0.896221764921742</v>
+        <v>-0.8962217649217458</v>
       </c>
       <c r="AC32" t="n">
-        <v>-2.093475860139583</v>
+        <v>-2.093475860139579</v>
       </c>
     </row>
     <row r="33">
@@ -4025,13 +3985,13 @@
         <v>3.3256</v>
       </c>
       <c r="AA33" t="n">
-        <v>-0.7141749022234251</v>
+        <v>-0.7141749022234227</v>
       </c>
       <c r="AB33" t="n">
         <v>-3.043865228640198</v>
       </c>
       <c r="AC33" t="n">
-        <v>-0.005296864219989163</v>
+        <v>-0.00529686421998253</v>
       </c>
     </row>
     <row r="34">
@@ -4132,13 +4092,13 @@
         <v>3.2581</v>
       </c>
       <c r="AA34" t="n">
-        <v>0.04861858855729813</v>
+        <v>0.04861858855729728</v>
       </c>
       <c r="AB34" t="n">
         <v>-1.162747121354752</v>
       </c>
       <c r="AC34" t="n">
-        <v>-0.4890148465405263</v>
+        <v>-0.4890148465405222</v>
       </c>
     </row>
     <row r="35">
@@ -4239,13 +4199,13 @@
         <v>3.9649</v>
       </c>
       <c r="AA35" t="n">
-        <v>-1.778947991006279</v>
+        <v>-1.778947991006278</v>
       </c>
       <c r="AB35" t="n">
-        <v>-1.040441992343174</v>
+        <v>-1.040441992343173</v>
       </c>
       <c r="AC35" t="n">
-        <v>1.041532487247059</v>
+        <v>1.041532487247064</v>
       </c>
     </row>
     <row r="36">
@@ -4346,13 +4306,13 @@
         <v>4.2193</v>
       </c>
       <c r="AA36" t="n">
-        <v>0.01518605994784407</v>
+        <v>0.01518605994784031</v>
       </c>
       <c r="AB36" t="n">
-        <v>2.811714154031113</v>
+        <v>2.81171415403111</v>
       </c>
       <c r="AC36" t="n">
-        <v>-1.704319286615018</v>
+        <v>-1.704319286615024</v>
       </c>
     </row>
     <row r="37">
@@ -4456,10 +4416,10 @@
         <v>1.36211647119868</v>
       </c>
       <c r="AB37" t="n">
-        <v>-0.316716017372852</v>
+        <v>-0.3167160173728507</v>
       </c>
       <c r="AC37" t="n">
-        <v>0.5085460616460202</v>
+        <v>0.5085460616460196</v>
       </c>
     </row>
     <row r="38">
@@ -4560,13 +4520,13 @@
         <v>3.8252</v>
       </c>
       <c r="AA38" t="n">
-        <v>1.601513749354949</v>
+        <v>1.601513749354946</v>
       </c>
       <c r="AB38" t="n">
-        <v>0.4133546075119571</v>
+        <v>0.413354607511955</v>
       </c>
       <c r="AC38" t="n">
-        <v>-1.140835144597442</v>
+        <v>-1.140835144597445</v>
       </c>
     </row>
     <row r="39">
@@ -4667,13 +4627,13 @@
         <v>3.2994</v>
       </c>
       <c r="AA39" t="n">
-        <v>-0.6534100463659753</v>
+        <v>-0.6534100463659772</v>
       </c>
       <c r="AB39" t="n">
-        <v>0.5607427012554287</v>
+        <v>0.5607427012554241</v>
       </c>
       <c r="AC39" t="n">
-        <v>-1.523566588153614</v>
+        <v>-1.523566588153612</v>
       </c>
     </row>
     <row r="40">
@@ -4774,13 +4734,13 @@
         <v>3.8668</v>
       </c>
       <c r="AA40" t="n">
-        <v>1.405050764760975</v>
+        <v>1.405050764760973</v>
       </c>
       <c r="AB40" t="n">
-        <v>0.8333046060838152</v>
+        <v>0.8333046060838153</v>
       </c>
       <c r="AC40" t="n">
-        <v>-0.06360960809628914</v>
+        <v>-0.06360960809629169</v>
       </c>
     </row>
     <row r="41">
@@ -4881,13 +4841,13 @@
         <v>2.8895</v>
       </c>
       <c r="AA41" t="n">
-        <v>0.7090193661667076</v>
+        <v>0.709019366166708</v>
       </c>
       <c r="AB41" t="n">
-        <v>0.9272477234162917</v>
+        <v>0.927247723416291</v>
       </c>
       <c r="AC41" t="n">
-        <v>-0.2608601727528611</v>
+        <v>-0.2608601727528637</v>
       </c>
     </row>
     <row r="42">
@@ -4991,10 +4951,10 @@
         <v>-1.149959500512955</v>
       </c>
       <c r="AB42" t="n">
-        <v>-0.533585263309636</v>
+        <v>-0.5335852633096336</v>
       </c>
       <c r="AC42" t="n">
-        <v>0.8776383195448785</v>
+        <v>0.8776383195448768</v>
       </c>
     </row>
     <row r="43">
@@ -5095,13 +5055,13 @@
         <v>3.3226</v>
       </c>
       <c r="AA43" t="n">
-        <v>-1.155539069983004</v>
+        <v>-1.155539069983005</v>
       </c>
       <c r="AB43" t="n">
-        <v>0.2971891836345071</v>
+        <v>0.297189183634507</v>
       </c>
       <c r="AC43" t="n">
-        <v>-0.1121569273927758</v>
+        <v>-0.1121569273927759</v>
       </c>
     </row>
     <row r="44">
@@ -5202,13 +5162,13 @@
         <v>4.0789</v>
       </c>
       <c r="AA44" t="n">
-        <v>1.823852456624049</v>
+        <v>1.823852456624046</v>
       </c>
       <c r="AB44" t="n">
-        <v>0.4705823656019973</v>
+        <v>0.4705823656019972</v>
       </c>
       <c r="AC44" t="n">
-        <v>-1.297787831976348</v>
+        <v>-1.29778783197635</v>
       </c>
     </row>
     <row r="45">
@@ -5309,13 +5269,13 @@
         <v>4.6109</v>
       </c>
       <c r="AA45" t="n">
-        <v>1.404639121194843</v>
+        <v>1.404639121194844</v>
       </c>
       <c r="AB45" t="n">
-        <v>0.1218440711086093</v>
+        <v>0.1218440711086136</v>
       </c>
       <c r="AC45" t="n">
-        <v>2.685832237883567</v>
+        <v>2.685832237883569</v>
       </c>
     </row>
     <row r="46">
@@ -5416,13 +5376,13 @@
         <v>3.9522</v>
       </c>
       <c r="AA46" t="n">
-        <v>0.1503851191214815</v>
+        <v>0.1503851191214834</v>
       </c>
       <c r="AB46" t="n">
-        <v>-0.7271794341353658</v>
+        <v>-0.7271794341353619</v>
       </c>
       <c r="AC46" t="n">
-        <v>1.934418568774975</v>
+        <v>1.934418568774976</v>
       </c>
     </row>
     <row r="47">
@@ -5523,13 +5483,13 @@
         <v>2.1252</v>
       </c>
       <c r="AA47" t="n">
-        <v>-1.840470918930225</v>
+        <v>-1.840470918930224</v>
       </c>
       <c r="AB47" t="n">
-        <v>-0.1769956561349026</v>
+        <v>-0.1769956561349039</v>
       </c>
       <c r="AC47" t="n">
-        <v>0.3168367212376101</v>
+        <v>0.3168367212376126</v>
       </c>
     </row>
     <row r="48">
@@ -5630,13 +5590,13 @@
         <v>4.8513</v>
       </c>
       <c r="AA48" t="n">
-        <v>0.5806764923458374</v>
+        <v>0.5806764923458383</v>
       </c>
       <c r="AB48" t="n">
-        <v>0.7706030148012166</v>
+        <v>0.7706030148012233</v>
       </c>
       <c r="AC48" t="n">
-        <v>2.946268051419253</v>
+        <v>2.946268051419251</v>
       </c>
     </row>
     <row r="49">
@@ -5737,13 +5697,13 @@
         <v>3.9717</v>
       </c>
       <c r="AA49" t="n">
-        <v>1.080261986609079</v>
+        <v>1.080261986609077</v>
       </c>
       <c r="AB49" t="n">
         <v>1.965793591045975</v>
       </c>
       <c r="AC49" t="n">
-        <v>0.1530196027215207</v>
+        <v>0.1530196027215154</v>
       </c>
     </row>
     <row r="50">
@@ -5844,13 +5804,13 @@
         <v>2.4505</v>
       </c>
       <c r="AA50" t="n">
-        <v>0.1104946485940693</v>
+        <v>0.1104946485940673</v>
       </c>
       <c r="AB50" t="n">
-        <v>0.2819478937670556</v>
+        <v>0.2819478937670533</v>
       </c>
       <c r="AC50" t="n">
-        <v>-0.5063059705638614</v>
+        <v>-0.5063059705638602</v>
       </c>
     </row>
     <row r="51">
@@ -5957,7 +5917,7 @@
         <v>1.602105392395269</v>
       </c>
       <c r="AC51" t="n">
-        <v>-0.07184151122301251</v>
+        <v>-0.07184151122301559</v>
       </c>
     </row>
     <row r="52">
@@ -6058,13 +6018,13 @@
         <v>2.687</v>
       </c>
       <c r="AA52" t="n">
-        <v>0.7539944731718154</v>
+        <v>0.7539944731718142</v>
       </c>
       <c r="AB52" t="n">
-        <v>0.8327456040872619</v>
+        <v>0.8327456040872622</v>
       </c>
       <c r="AC52" t="n">
-        <v>-0.3339149407051668</v>
+        <v>-0.3339149407051691</v>
       </c>
     </row>
     <row r="53">
@@ -6165,13 +6125,13 @@
         <v>3.8108</v>
       </c>
       <c r="AA53" t="n">
-        <v>-0.2761982014018979</v>
+        <v>-0.2761982014019017</v>
       </c>
       <c r="AB53" t="n">
         <v>1.99911236534779</v>
       </c>
       <c r="AC53" t="n">
-        <v>0.5134924996480387</v>
+        <v>0.5134924996480356</v>
       </c>
     </row>
     <row r="54">
@@ -6272,13 +6232,13 @@
         <v>3.0372</v>
       </c>
       <c r="AA54" t="n">
-        <v>1.238909919868286</v>
+        <v>1.238909919868284</v>
       </c>
       <c r="AB54" t="n">
         <v>0.4737305413103299</v>
       </c>
       <c r="AC54" t="n">
-        <v>-0.7916990526659518</v>
+        <v>-0.7916990526659552</v>
       </c>
     </row>
     <row r="55">
@@ -6382,10 +6342,10 @@
         <v>-0.2852531219257626</v>
       </c>
       <c r="AB55" t="n">
-        <v>1.291474628034831</v>
+        <v>1.291474628034829</v>
       </c>
       <c r="AC55" t="n">
-        <v>0.5545626449134012</v>
+        <v>0.5545626449134019</v>
       </c>
     </row>
     <row r="56">
@@ -6486,13 +6446,13 @@
         <v>3.1348</v>
       </c>
       <c r="AA56" t="n">
-        <v>-0.3907615437754368</v>
+        <v>-0.3907615437754363</v>
       </c>
       <c r="AB56" t="n">
-        <v>1.11956204291631</v>
+        <v>1.119562042916307</v>
       </c>
       <c r="AC56" t="n">
-        <v>-0.5618462983993964</v>
+        <v>-0.5618462983993967</v>
       </c>
     </row>
     <row r="57">
@@ -6593,13 +6553,13 @@
         <v>4.4655</v>
       </c>
       <c r="AA57" t="n">
-        <v>1.308217160626507</v>
+        <v>1.308217160626508</v>
       </c>
       <c r="AB57" t="n">
-        <v>0.3522721690162212</v>
+        <v>0.3522721690162255</v>
       </c>
       <c r="AC57" t="n">
-        <v>2.586143108818242</v>
+        <v>2.58614310881824</v>
       </c>
     </row>
     <row r="58">
@@ -6700,13 +6660,13 @@
         <v>4.7631</v>
       </c>
       <c r="AA58" t="n">
-        <v>-0.210079998715986</v>
+        <v>-0.2100799987159829</v>
       </c>
       <c r="AB58" t="n">
-        <v>1.9146441701103</v>
+        <v>1.914644170110303</v>
       </c>
       <c r="AC58" t="n">
-        <v>1.741600752236656</v>
+        <v>1.741600752236655</v>
       </c>
     </row>
     <row r="59">
@@ -6807,13 +6767,13 @@
         <v>2.8766</v>
       </c>
       <c r="AA59" t="n">
-        <v>-1.313662711499062</v>
+        <v>-1.313662711499063</v>
       </c>
       <c r="AB59" t="n">
-        <v>-0.8629142767849342</v>
+        <v>-0.8629142767849363</v>
       </c>
       <c r="AC59" t="n">
-        <v>-0.3949296967426061</v>
+        <v>-0.3949296967426026</v>
       </c>
     </row>
     <row r="60">
@@ -6914,13 +6874,13 @@
         <v>3.331</v>
       </c>
       <c r="AA60" t="n">
-        <v>0.009974925744017109</v>
+        <v>0.009974925744014705</v>
       </c>
       <c r="AB60" t="n">
-        <v>-0.8441611480863994</v>
+        <v>-0.8441611480864032</v>
       </c>
       <c r="AC60" t="n">
-        <v>-1.574209066162615</v>
+        <v>-1.574209066162611</v>
       </c>
     </row>
     <row r="61">
@@ -7021,13 +6981,13 @@
         <v>2.3733</v>
       </c>
       <c r="AA61" t="n">
-        <v>-1.127453946351195</v>
+        <v>-1.127453946351197</v>
       </c>
       <c r="AB61" t="n">
-        <v>1.286374777842267</v>
+        <v>1.286374777842264</v>
       </c>
       <c r="AC61" t="n">
-        <v>-0.6766329976760591</v>
+        <v>-0.6766329976760603</v>
       </c>
     </row>
     <row r="62">
@@ -7128,13 +7088,13 @@
         <v>4.8475</v>
       </c>
       <c r="AA62" t="n">
-        <v>0.1163652129796151</v>
+        <v>0.1163652129796182</v>
       </c>
       <c r="AB62" t="n">
-        <v>-1.989884322523801</v>
+        <v>-1.989884322523795</v>
       </c>
       <c r="AC62" t="n">
-        <v>3.464561459383454</v>
+        <v>3.46456145938346</v>
       </c>
     </row>
     <row r="63">
@@ -7238,10 +7198,10 @@
         <v>1.930117691055209</v>
       </c>
       <c r="AB63" t="n">
-        <v>-1.207121274404577</v>
+        <v>-1.207121274404576</v>
       </c>
       <c r="AC63" t="n">
-        <v>0.6870130068201891</v>
+        <v>0.6870130068201931</v>
       </c>
     </row>
     <row r="64">
@@ -7342,13 +7302,13 @@
         <v>2.3036</v>
       </c>
       <c r="AA64" t="n">
-        <v>0.1766077492985817</v>
+        <v>0.1766077492985805</v>
       </c>
       <c r="AB64" t="n">
-        <v>0.0452837209645989</v>
+        <v>0.04528372096459691</v>
       </c>
       <c r="AC64" t="n">
-        <v>-0.9104953201298195</v>
+        <v>-0.9104953201298204</v>
       </c>
     </row>
     <row r="65">
@@ -7449,13 +7409,13 @@
         <v>2.641</v>
       </c>
       <c r="AA65" t="n">
-        <v>0.4894004923463648</v>
+        <v>0.4894004923463646</v>
       </c>
       <c r="AB65" t="n">
-        <v>0.4982050945548226</v>
+        <v>0.4982050945548218</v>
       </c>
       <c r="AC65" t="n">
-        <v>-1.173120471534516</v>
+        <v>-1.173120471534518</v>
       </c>
     </row>
     <row r="66">
@@ -7556,13 +7516,13 @@
         <v>2.9409</v>
       </c>
       <c r="AA66" t="n">
-        <v>-1.485643507183447</v>
+        <v>-1.485643507183445</v>
       </c>
       <c r="AB66" t="n">
-        <v>0.09736638394406842</v>
+        <v>0.09736638394406379</v>
       </c>
       <c r="AC66" t="n">
-        <v>-1.365929152239662</v>
+        <v>-1.365929152239663</v>
       </c>
     </row>
     <row r="67">
@@ -7663,13 +7623,13 @@
         <v>2.1544</v>
       </c>
       <c r="AA67" t="n">
-        <v>-0.527726300387842</v>
+        <v>-0.5277263003878426</v>
       </c>
       <c r="AB67" t="n">
-        <v>0.2086883971808541</v>
+        <v>0.2086883971808524</v>
       </c>
       <c r="AC67" t="n">
-        <v>-1.277098317262224</v>
+        <v>-1.277098317262228</v>
       </c>
     </row>
     <row r="68">
@@ -7770,13 +7730,13 @@
         <v>3.1799</v>
       </c>
       <c r="AA68" t="n">
-        <v>-0.627443679163226</v>
+        <v>-0.6274436791632267</v>
       </c>
       <c r="AB68" t="n">
-        <v>0.2745248219087882</v>
+        <v>0.2745248219087912</v>
       </c>
       <c r="AC68" t="n">
-        <v>1.155180627209635</v>
+        <v>1.155180627209633</v>
       </c>
     </row>
     <row r="69">
@@ -7877,13 +7837,13 @@
         <v>4.1919</v>
       </c>
       <c r="AA69" t="n">
-        <v>0.9067056694315134</v>
+        <v>0.9067056694315112</v>
       </c>
       <c r="AB69" t="n">
-        <v>-0.497302394171609</v>
+        <v>-0.4973023941716052</v>
       </c>
       <c r="AC69" t="n">
-        <v>2.04017923796284</v>
+        <v>2.040179237962841</v>
       </c>
     </row>
     <row r="70">
@@ -7984,13 +7944,13 @@
         <v>3.6979</v>
       </c>
       <c r="AA70" t="n">
-        <v>1.741772403604564</v>
+        <v>1.741772403604561</v>
       </c>
       <c r="AB70" t="n">
-        <v>-0.38549750327009</v>
+        <v>-0.3854975032700897</v>
       </c>
       <c r="AC70" t="n">
-        <v>-0.6126001396279469</v>
+        <v>-0.6126001396279486</v>
       </c>
     </row>
     <row r="71">
@@ -8091,13 +8051,13 @@
         <v>3.6152</v>
       </c>
       <c r="AA71" t="n">
-        <v>0.2191533415221321</v>
+        <v>0.2191533415221314</v>
       </c>
       <c r="AB71" t="n">
-        <v>0.3542934812001161</v>
+        <v>0.3542934812001177</v>
       </c>
       <c r="AC71" t="n">
-        <v>1.606111465194901</v>
+        <v>1.606111465194902</v>
       </c>
     </row>
     <row r="72">
@@ -8198,13 +8158,13 @@
         <v>3.9201</v>
       </c>
       <c r="AA72" t="n">
-        <v>1.319163259940494</v>
+        <v>1.319163259940491</v>
       </c>
       <c r="AB72" t="n">
-        <v>0.3607558380933203</v>
+        <v>0.3607558380933202</v>
       </c>
       <c r="AC72" t="n">
-        <v>-0.3107387339014924</v>
+        <v>-0.3107387339014901</v>
       </c>
     </row>
     <row r="73">
@@ -8305,13 +8265,13 @@
         <v>3.1802</v>
       </c>
       <c r="AA73" t="n">
-        <v>0.8702518195863719</v>
+        <v>0.87025181958637</v>
       </c>
       <c r="AB73" t="n">
-        <v>0.2139158588640824</v>
+        <v>0.2139158588640815</v>
       </c>
       <c r="AC73" t="n">
-        <v>-0.4606795193589294</v>
+        <v>-0.4606795193589319</v>
       </c>
     </row>
     <row r="74">
@@ -8412,13 +8372,13 @@
         <v>3.794</v>
       </c>
       <c r="AA74" t="n">
-        <v>0.272694247453094</v>
+        <v>0.2726942474530901</v>
       </c>
       <c r="AB74" t="n">
         <v>2.097136567442131</v>
       </c>
       <c r="AC74" t="n">
-        <v>-0.07927043107286712</v>
+        <v>-0.07927043107286987</v>
       </c>
     </row>
     <row r="75">
@@ -8519,13 +8479,13 @@
         <v>4.0178</v>
       </c>
       <c r="AA75" t="n">
-        <v>0.7104562916219099</v>
+        <v>0.710456291621909</v>
       </c>
       <c r="AB75" t="n">
-        <v>0.604218687035304</v>
+        <v>0.6042186870353049</v>
       </c>
       <c r="AC75" t="n">
-        <v>0.7213915363064173</v>
+        <v>0.7213915363064179</v>
       </c>
     </row>
     <row r="76">
@@ -8626,13 +8586,13 @@
         <v>3.8928</v>
       </c>
       <c r="AA76" t="n">
-        <v>0.6738268541686695</v>
+        <v>0.6738268541686711</v>
       </c>
       <c r="AB76" t="n">
-        <v>0.7845956846479987</v>
+        <v>0.7845956846480013</v>
       </c>
       <c r="AC76" t="n">
-        <v>0.3336731947203288</v>
+        <v>0.3336731947203254</v>
       </c>
     </row>
     <row r="77">
@@ -8733,13 +8693,13 @@
         <v>3.8345</v>
       </c>
       <c r="AA77" t="n">
-        <v>-0.08360111235421235</v>
+        <v>-0.08360111235421162</v>
       </c>
       <c r="AB77" t="n">
-        <v>1.25413801642788</v>
+        <v>1.254138016427884</v>
       </c>
       <c r="AC77" t="n">
-        <v>1.539142157807012</v>
+        <v>1.539142157807009</v>
       </c>
     </row>
     <row r="78">
@@ -8840,13 +8800,13 @@
         <v>2.8688</v>
       </c>
       <c r="AA78" t="n">
-        <v>-0.9190576615302927</v>
+        <v>-0.9190576615302932</v>
       </c>
       <c r="AB78" t="n">
-        <v>-0.1162923377995224</v>
+        <v>-0.1162923377995228</v>
       </c>
       <c r="AC78" t="n">
-        <v>-0.3592340887988962</v>
+        <v>-0.3592340887988976</v>
       </c>
     </row>
     <row r="79">
@@ -8947,13 +8907,13 @@
         <v>4.4096</v>
       </c>
       <c r="AA79" t="n">
-        <v>0.5661940310269158</v>
+        <v>0.5661940310269186</v>
       </c>
       <c r="AB79" t="n">
-        <v>1.358651772281746</v>
+        <v>1.358651772281749</v>
       </c>
       <c r="AC79" t="n">
-        <v>1.587420849729533</v>
+        <v>1.587420849729531</v>
       </c>
     </row>
     <row r="80">
@@ -9054,13 +9014,13 @@
         <v>2.741</v>
       </c>
       <c r="AA80" t="n">
-        <v>-0.4579612552722921</v>
+        <v>-0.4579612552722925</v>
       </c>
       <c r="AB80" t="n">
-        <v>0.6115254171536854</v>
+        <v>0.611525417153687</v>
       </c>
       <c r="AC80" t="n">
-        <v>1.092567170695878</v>
+        <v>1.092567170695875</v>
       </c>
     </row>
     <row r="81">
@@ -9164,10 +9124,10 @@
         <v>2.581884900072124</v>
       </c>
       <c r="AB81" t="n">
-        <v>-0.02226876223297612</v>
+        <v>-0.02226876223297761</v>
       </c>
       <c r="AC81" t="n">
-        <v>-1.686949897935901</v>
+        <v>-1.6869498979359</v>
       </c>
     </row>
     <row r="82">
@@ -9268,13 +9228,13 @@
         <v>3.3762</v>
       </c>
       <c r="AA82" t="n">
-        <v>-0.8286855035846648</v>
+        <v>-0.828685503584667</v>
       </c>
       <c r="AB82" t="n">
-        <v>-1.225636198133535</v>
+        <v>-1.225636198133537</v>
       </c>
       <c r="AC82" t="n">
-        <v>-0.8104474211091794</v>
+        <v>-0.8104474211091764</v>
       </c>
     </row>
     <row r="83">
@@ -9375,13 +9335,13 @@
         <v>4.1023</v>
       </c>
       <c r="AA83" t="n">
-        <v>0.5346233750340732</v>
+        <v>0.5346233750340714</v>
       </c>
       <c r="AB83" t="n">
-        <v>1.811610721393705</v>
+        <v>1.811610721393706</v>
       </c>
       <c r="AC83" t="n">
-        <v>1.439663771737915</v>
+        <v>1.439663771737911</v>
       </c>
     </row>
     <row r="84">
@@ -9482,13 +9442,13 @@
         <v>4.1149</v>
       </c>
       <c r="AA84" t="n">
-        <v>0.3216882384885552</v>
+        <v>0.3216882384885566</v>
       </c>
       <c r="AB84" t="n">
         <v>-2.357747743115827</v>
       </c>
       <c r="AC84" t="n">
-        <v>-0.2699373082487631</v>
+        <v>-0.2699373082487584</v>
       </c>
     </row>
     <row r="85">
@@ -9589,13 +9549,13 @@
         <v>3.3982</v>
       </c>
       <c r="AA85" t="n">
-        <v>-0.1961535238301202</v>
+        <v>-0.1961535238301199</v>
       </c>
       <c r="AB85" t="n">
-        <v>0.4964972482026036</v>
+        <v>0.4964972482026056</v>
       </c>
       <c r="AC85" t="n">
-        <v>1.884308364444071</v>
+        <v>1.884308364444073</v>
       </c>
     </row>
     <row r="86">
@@ -9696,13 +9656,13 @@
         <v>5.0216</v>
       </c>
       <c r="AA86" t="n">
-        <v>2.61346821226939</v>
+        <v>2.613468212269388</v>
       </c>
       <c r="AB86" t="n">
-        <v>-1.611173399614311</v>
+        <v>-1.61117339961431</v>
       </c>
       <c r="AC86" t="n">
-        <v>-0.1263129649607902</v>
+        <v>-0.1263129649607831</v>
       </c>
     </row>
     <row r="87">
@@ -9803,13 +9763,13 @@
         <v>3.7457</v>
       </c>
       <c r="AA87" t="n">
-        <v>1.497828363416132</v>
+        <v>1.49782836341613</v>
       </c>
       <c r="AB87" t="n">
-        <v>0.3801682773501168</v>
+        <v>0.3801682773501177</v>
       </c>
       <c r="AC87" t="n">
-        <v>0.838489962252264</v>
+        <v>0.838489962252266</v>
       </c>
     </row>
     <row r="88">
@@ -9910,13 +9870,13 @@
         <v>3.004</v>
       </c>
       <c r="AA88" t="n">
-        <v>-0.6556123964246906</v>
+        <v>-0.6556123964246899</v>
       </c>
       <c r="AB88" t="n">
-        <v>0.5272270894180452</v>
+        <v>0.5272270894180466</v>
       </c>
       <c r="AC88" t="n">
-        <v>0.1442876191452494</v>
+        <v>0.1442876191452473</v>
       </c>
     </row>
     <row r="89">
@@ -10017,13 +9977,13 @@
         <v>4.0637</v>
       </c>
       <c r="AA89" t="n">
-        <v>1.051659308042348</v>
+        <v>1.051659308042351</v>
       </c>
       <c r="AB89" t="n">
-        <v>-1.28878030225289</v>
+        <v>-1.288780302252887</v>
       </c>
       <c r="AC89" t="n">
-        <v>0.851350604131521</v>
+        <v>0.8513506041315227</v>
       </c>
     </row>
     <row r="90">
@@ -10124,13 +10084,13 @@
         <v>3.1583</v>
       </c>
       <c r="AA90" t="n">
-        <v>-0.07533305655329452</v>
+        <v>-0.07533305655329574</v>
       </c>
       <c r="AB90" t="n">
-        <v>-0.07084121845527352</v>
+        <v>-0.07084121845527035</v>
       </c>
       <c r="AC90" t="n">
-        <v>0.6111105543584526</v>
+        <v>0.6111105543584509</v>
       </c>
     </row>
     <row r="91">
@@ -10231,13 +10191,13 @@
         <v>2.2504</v>
       </c>
       <c r="AA91" t="n">
-        <v>-1.318544496516709</v>
+        <v>-1.318544496516708</v>
       </c>
       <c r="AB91" t="n">
-        <v>0.04717099132322171</v>
+        <v>0.04717099132322032</v>
       </c>
       <c r="AC91" t="n">
-        <v>-1.002941345113912</v>
+        <v>-1.002941345113913</v>
       </c>
     </row>
     <row r="92">
@@ -10338,13 +10298,13 @@
         <v>4.1769</v>
       </c>
       <c r="AA92" t="n">
-        <v>1.899636388582811</v>
+        <v>1.899636388582809</v>
       </c>
       <c r="AB92" t="n">
         <v>-1.183875906561255</v>
       </c>
       <c r="AC92" t="n">
-        <v>-0.9637462732868453</v>
+        <v>-0.9637462732868455</v>
       </c>
     </row>
     <row r="93">
@@ -10445,13 +10405,13 @@
         <v>3.8748</v>
       </c>
       <c r="AA93" t="n">
-        <v>0.07151594385507008</v>
+        <v>0.07151594385506969</v>
       </c>
       <c r="AB93" t="n">
-        <v>2.578561718647216</v>
+        <v>2.578561718647214</v>
       </c>
       <c r="AC93" t="n">
-        <v>-0.4115705121057425</v>
+        <v>-0.411570512105746</v>
       </c>
     </row>
     <row r="94">
@@ -10552,13 +10512,13 @@
         <v>4.5775</v>
       </c>
       <c r="AA94" t="n">
-        <v>2.218890880492956</v>
+        <v>2.218890880492957</v>
       </c>
       <c r="AB94" t="n">
-        <v>0.3852280034672623</v>
+        <v>0.385228003467261</v>
       </c>
       <c r="AC94" t="n">
-        <v>-0.2947525213252485</v>
+        <v>-0.2947525213252484</v>
       </c>
     </row>
     <row r="95">
@@ -10659,13 +10619,13 @@
         <v>3.8489</v>
       </c>
       <c r="AA95" t="n">
-        <v>1.385788249201439</v>
+        <v>1.38578824920144</v>
       </c>
       <c r="AB95" t="n">
-        <v>-0.753092781944261</v>
+        <v>-0.7530927819442621</v>
       </c>
       <c r="AC95" t="n">
-        <v>-0.02995660640232624</v>
+        <v>-0.02995660640232203</v>
       </c>
     </row>
     <row r="96">
@@ -10766,13 +10726,13 @@
         <v>3.6339</v>
       </c>
       <c r="AA96" t="n">
-        <v>1.770312156264694</v>
+        <v>1.770312156264691</v>
       </c>
       <c r="AB96" t="n">
-        <v>1.177605229914975</v>
+        <v>1.177605229914976</v>
       </c>
       <c r="AC96" t="n">
-        <v>0.2932619097954454</v>
+        <v>0.2932619097954415</v>
       </c>
     </row>
     <row r="97">
@@ -10873,10 +10833,10 @@
         <v>3.2019</v>
       </c>
       <c r="AA97" t="n">
-        <v>1.336066435213874</v>
+        <v>1.336066435213872</v>
       </c>
       <c r="AB97" t="n">
-        <v>0.0977600958189737</v>
+        <v>0.09776009581897144</v>
       </c>
       <c r="AC97" t="n">
         <v>-1.17756631374119</v>
@@ -10980,13 +10940,13 @@
         <v>4.0692</v>
       </c>
       <c r="AA98" t="n">
-        <v>0.2756049386200713</v>
+        <v>0.2756049386200733</v>
       </c>
       <c r="AB98" t="n">
-        <v>-2.435577321617046</v>
+        <v>-2.435577321617044</v>
       </c>
       <c r="AC98" t="n">
-        <v>-0.7108054683586048</v>
+        <v>-0.7108054683586029</v>
       </c>
     </row>
     <row r="99">
@@ -11087,13 +11047,13 @@
         <v>3.7718</v>
       </c>
       <c r="AA99" t="n">
-        <v>1.467509403449668</v>
+        <v>1.467509403449666</v>
       </c>
       <c r="AB99" t="n">
-        <v>-0.6057645443997108</v>
+        <v>-0.6057645443997109</v>
       </c>
       <c r="AC99" t="n">
-        <v>-0.1674473159740103</v>
+        <v>-0.1674473159740083</v>
       </c>
     </row>
     <row r="100">
@@ -11194,13 +11154,13 @@
         <v>3.1559</v>
       </c>
       <c r="AA100" t="n">
-        <v>-1.308438544523169</v>
+        <v>-1.308438544523168</v>
       </c>
       <c r="AB100" t="n">
-        <v>0.06185852426236534</v>
+        <v>0.06185852426236414</v>
       </c>
       <c r="AC100" t="n">
-        <v>-0.0227355767722194</v>
+        <v>-0.02273557677222078</v>
       </c>
     </row>
     <row r="101">
@@ -11301,13 +11261,13 @@
         <v>2.6601</v>
       </c>
       <c r="AA101" t="n">
-        <v>-0.4400980061283889</v>
+        <v>-0.4400980061283867</v>
       </c>
       <c r="AB101" t="n">
-        <v>1.016399689534804</v>
+        <v>1.016399689534805</v>
       </c>
       <c r="AC101" t="n">
-        <v>1.057015511088031</v>
+        <v>1.05701551108803</v>
       </c>
     </row>
     <row r="102">
@@ -11408,13 +11368,13 @@
         <v>3.4093</v>
       </c>
       <c r="AA102" t="n">
-        <v>-1.209624263265898</v>
+        <v>-1.209624263265894</v>
       </c>
       <c r="AB102" t="n">
-        <v>1.049510819070179</v>
+        <v>1.04951081907018</v>
       </c>
       <c r="AC102" t="n">
-        <v>0.7789324271357118</v>
+        <v>0.7789324271357121</v>
       </c>
     </row>
     <row r="103">
@@ -11515,13 +11475,13 @@
         <v>4.2697</v>
       </c>
       <c r="AA103" t="n">
-        <v>1.608953990006806</v>
+        <v>1.608953990006804</v>
       </c>
       <c r="AB103" t="n">
-        <v>0.2851511731508149</v>
+        <v>0.2851511731508163</v>
       </c>
       <c r="AC103" t="n">
-        <v>0.6913902397132506</v>
+        <v>0.691390239713247</v>
       </c>
     </row>
     <row r="104">
@@ -11622,13 +11582,13 @@
         <v>3.2064</v>
       </c>
       <c r="AA104" t="n">
-        <v>-0.4474091399221843</v>
+        <v>-0.4474091399221859</v>
       </c>
       <c r="AB104" t="n">
-        <v>1.594189355922977</v>
+        <v>1.594189355922978</v>
       </c>
       <c r="AC104" t="n">
-        <v>0.8594005120169689</v>
+        <v>0.8594005120169638</v>
       </c>
     </row>
     <row r="105">
@@ -11729,13 +11689,13 @@
         <v>2.6392</v>
       </c>
       <c r="AA105" t="n">
-        <v>-0.216808924768832</v>
+        <v>-0.2168089247688328</v>
       </c>
       <c r="AB105" t="n">
-        <v>-0.1939661247023683</v>
+        <v>-0.1939661247023706</v>
       </c>
       <c r="AC105" t="n">
-        <v>-0.5438840218552239</v>
+        <v>-0.543884021855223</v>
       </c>
     </row>
     <row r="106">
@@ -11836,13 +11796,13 @@
         <v>4.0546</v>
       </c>
       <c r="AA106" t="n">
-        <v>0.9599587203217328</v>
+        <v>0.9599587203217335</v>
       </c>
       <c r="AB106" t="n">
-        <v>-0.4374533112949151</v>
+        <v>-0.4374533112949123</v>
       </c>
       <c r="AC106" t="n">
-        <v>2.096078880792295</v>
+        <v>2.0960788807923</v>
       </c>
     </row>
     <row r="107">
@@ -11946,7 +11906,7 @@
         <v>-1.661803265537111</v>
       </c>
       <c r="AB107" t="n">
-        <v>-0.0572843570341131</v>
+        <v>-0.05728435703411443</v>
       </c>
       <c r="AC107" t="n">
         <v>-0.364930179197325</v>
@@ -12050,13 +12010,13 @@
         <v>2.7888</v>
       </c>
       <c r="AA108" t="n">
-        <v>-0.1097138131759374</v>
+        <v>-0.1097138131759366</v>
       </c>
       <c r="AB108" t="n">
         <v>-1.344106384737189</v>
       </c>
       <c r="AC108" t="n">
-        <v>-0.6111820375496524</v>
+        <v>-0.6111820375496535</v>
       </c>
     </row>
     <row r="109">
@@ -12157,13 +12117,13 @@
         <v>2.8297</v>
       </c>
       <c r="AA109" t="n">
-        <v>0.2841829134137791</v>
+        <v>0.2841829134137769</v>
       </c>
       <c r="AB109" t="n">
-        <v>0.8149995432065239</v>
+        <v>0.814999543206522</v>
       </c>
       <c r="AC109" t="n">
-        <v>-0.8235855504631152</v>
+        <v>-0.8235855504631184</v>
       </c>
     </row>
     <row r="110">
@@ -12264,13 +12224,13 @@
         <v>5.3663</v>
       </c>
       <c r="AA110" t="n">
-        <v>1.825573680021751</v>
+        <v>1.825573680021752</v>
       </c>
       <c r="AB110" t="n">
-        <v>-1.38090610897832</v>
+        <v>-1.380906108978313</v>
       </c>
       <c r="AC110" t="n">
-        <v>1.765207962408784</v>
+        <v>1.765207962408786</v>
       </c>
     </row>
     <row r="111">
@@ -12371,10 +12331,10 @@
         <v>4.0632</v>
       </c>
       <c r="AA111" t="n">
-        <v>0.5258673229575181</v>
+        <v>0.5258673229575173</v>
       </c>
       <c r="AB111" t="n">
-        <v>1.038532569329357</v>
+        <v>1.038532569329353</v>
       </c>
       <c r="AC111" t="n">
         <v>-1.298476574297051</v>
@@ -12478,10 +12438,10 @@
         <v>4.0285</v>
       </c>
       <c r="AA112" t="n">
-        <v>-0.02289403957554718</v>
+        <v>-0.02289403957554815</v>
       </c>
       <c r="AB112" t="n">
-        <v>-1.184328255296998</v>
+        <v>-1.184328255296999</v>
       </c>
       <c r="AC112" t="n">
         <v>-2.519172715255776</v>
@@ -12585,13 +12545,13 @@
         <v>3.3988</v>
       </c>
       <c r="AA113" t="n">
-        <v>0.07066598798929231</v>
+        <v>0.0706659879892918</v>
       </c>
       <c r="AB113" t="n">
-        <v>-0.6043021899088764</v>
+        <v>-0.6043021899088779</v>
       </c>
       <c r="AC113" t="n">
-        <v>-1.469679218932374</v>
+        <v>-1.469679218932378</v>
       </c>
     </row>
     <row r="114">
@@ -12692,10 +12652,10 @@
         <v>3.6508</v>
       </c>
       <c r="AA114" t="n">
-        <v>-0.05105107419381434</v>
+        <v>-0.05105107419381129</v>
       </c>
       <c r="AB114" t="n">
-        <v>-1.367394715575102</v>
+        <v>-1.367394715575097</v>
       </c>
       <c r="AC114" t="n">
         <v>1.608922747581153</v>
@@ -12799,13 +12759,13 @@
         <v>2.5149</v>
       </c>
       <c r="AA115" t="n">
-        <v>-2.022143479741883</v>
+        <v>-2.022143479741885</v>
       </c>
       <c r="AB115" t="n">
-        <v>1.711051595066849</v>
+        <v>1.711051595066847</v>
       </c>
       <c r="AC115" t="n">
-        <v>0.3011156004676174</v>
+        <v>0.3011156004676163</v>
       </c>
     </row>
     <row r="116">
@@ -12906,13 +12866,13 @@
         <v>4.0211</v>
       </c>
       <c r="AA116" t="n">
-        <v>-0.1335781870236918</v>
+        <v>-0.1335781870236913</v>
       </c>
       <c r="AB116" t="n">
-        <v>-0.004932991507301076</v>
+        <v>-0.004932991507297689</v>
       </c>
       <c r="AC116" t="n">
-        <v>1.660107326071337</v>
+        <v>1.660107326071338</v>
       </c>
     </row>
     <row r="117">
@@ -13013,13 +12973,13 @@
         <v>4.5979</v>
       </c>
       <c r="AA117" t="n">
-        <v>0.678111960327732</v>
+        <v>0.6781119603277324</v>
       </c>
       <c r="AB117" t="n">
-        <v>-1.701610321704202</v>
+        <v>-1.701610321704208</v>
       </c>
       <c r="AC117" t="n">
-        <v>-3.436956245293572</v>
+        <v>-3.43695624529357</v>
       </c>
     </row>
     <row r="118">
@@ -13120,13 +13080,13 @@
         <v>3.7934</v>
       </c>
       <c r="AA118" t="n">
-        <v>1.450530202458622</v>
+        <v>1.45053020245862</v>
       </c>
       <c r="AB118" t="n">
-        <v>0.9669904953991999</v>
+        <v>0.9669904953991978</v>
       </c>
       <c r="AC118" t="n">
-        <v>-0.893588820766029</v>
+        <v>-0.8935888207660313</v>
       </c>
     </row>
     <row r="119">
@@ -13227,13 +13187,13 @@
         <v>2.5327</v>
       </c>
       <c r="AA119" t="n">
-        <v>-1.102702580511912</v>
+        <v>-1.102702580511913</v>
       </c>
       <c r="AB119" t="n">
         <v>1.375621572292457</v>
       </c>
       <c r="AC119" t="n">
-        <v>0.2611995959372611</v>
+        <v>0.261199595937256</v>
       </c>
     </row>
     <row r="120">
@@ -13334,13 +13294,13 @@
         <v>4.4183</v>
       </c>
       <c r="AA120" t="n">
-        <v>0.1785449297255632</v>
+        <v>0.178544929725563</v>
       </c>
       <c r="AB120" t="n">
-        <v>-0.6403741671467961</v>
+        <v>-0.6403741671467911</v>
       </c>
       <c r="AC120" t="n">
-        <v>2.966477307643165</v>
+        <v>2.966477307643167</v>
       </c>
     </row>
     <row r="121">
@@ -13441,13 +13401,13 @@
         <v>2.7897</v>
       </c>
       <c r="AA121" t="n">
-        <v>-0.2217883392659042</v>
+        <v>-0.221788339265904</v>
       </c>
       <c r="AB121" t="n">
-        <v>-0.8865164678769653</v>
+        <v>-0.886516467876968</v>
       </c>
       <c r="AC121" t="n">
-        <v>-1.293640591362531</v>
+        <v>-1.293640591362532</v>
       </c>
     </row>
     <row r="122">
@@ -13548,13 +13508,13 @@
         <v>3.668</v>
       </c>
       <c r="AA122" t="n">
-        <v>-0.7443222326617184</v>
+        <v>-0.7443222326617198</v>
       </c>
       <c r="AB122" t="n">
-        <v>-0.4852012390274534</v>
+        <v>-0.4852012390274515</v>
       </c>
       <c r="AC122" t="n">
-        <v>0.8163030781524557</v>
+        <v>0.8163030781524533</v>
       </c>
     </row>
     <row r="123">
@@ -13655,13 +13615,13 @@
         <v>2.9793</v>
       </c>
       <c r="AA123" t="n">
-        <v>-0.5558373339887857</v>
+        <v>-0.5558373339887871</v>
       </c>
       <c r="AB123" t="n">
-        <v>0.6397841726431779</v>
+        <v>0.6397841726431763</v>
       </c>
       <c r="AC123" t="n">
-        <v>-1.494279392977787</v>
+        <v>-1.49427939297779</v>
       </c>
     </row>
     <row r="124">
@@ -13762,13 +13722,13 @@
         <v>5.0342</v>
       </c>
       <c r="AA124" t="n">
-        <v>2.013279509360682</v>
+        <v>2.013279509360686</v>
       </c>
       <c r="AB124" t="n">
-        <v>-2.345412543199414</v>
+        <v>-2.34541254319941</v>
       </c>
       <c r="AC124" t="n">
-        <v>1.033267975957385</v>
+        <v>1.03326797595739</v>
       </c>
     </row>
     <row r="125">
@@ -13869,13 +13829,13 @@
         <v>5.7381</v>
       </c>
       <c r="AA125" t="n">
-        <v>3.422501411251484</v>
+        <v>3.422501411251482</v>
       </c>
       <c r="AB125" t="n">
-        <v>1.312559187825466</v>
+        <v>1.312559187825467</v>
       </c>
       <c r="AC125" t="n">
-        <v>-1.224060159517692</v>
+        <v>-1.224060159517696</v>
       </c>
     </row>
     <row r="126">
@@ -13976,13 +13936,13 @@
         <v>5.0691</v>
       </c>
       <c r="AA126" t="n">
-        <v>1.035200878611652</v>
+        <v>1.035200878611655</v>
       </c>
       <c r="AB126" t="n">
-        <v>0.2800623376951881</v>
+        <v>0.2800623376951965</v>
       </c>
       <c r="AC126" t="n">
-        <v>3.456188008721661</v>
+        <v>3.45618800872166</v>
       </c>
     </row>
     <row r="127">
@@ -14083,13 +14043,13 @@
         <v>4.6204</v>
       </c>
       <c r="AA127" t="n">
-        <v>0.6243026434272144</v>
+        <v>0.6243026434272126</v>
       </c>
       <c r="AB127" t="n">
-        <v>-2.305324326336733</v>
+        <v>-2.305324326336734</v>
       </c>
       <c r="AC127" t="n">
-        <v>-1.339889301702382</v>
+        <v>-1.339889301702379</v>
       </c>
     </row>
     <row r="128">
@@ -14193,10 +14153,10 @@
         <v>1.050375899192933</v>
       </c>
       <c r="AB128" t="n">
-        <v>0.2970916691828093</v>
+        <v>0.2970916691828098</v>
       </c>
       <c r="AC128" t="n">
-        <v>0.1804896674730973</v>
+        <v>0.1804896674730965</v>
       </c>
     </row>
     <row r="129">
@@ -14297,13 +14257,13 @@
         <v>4.4556</v>
       </c>
       <c r="AA129" t="n">
-        <v>0.2097497229916588</v>
+        <v>0.2097497229916607</v>
       </c>
       <c r="AB129" t="n">
-        <v>-2.796315400615454</v>
+        <v>-2.79631540061545</v>
       </c>
       <c r="AC129" t="n">
-        <v>0.9435269834753152</v>
+        <v>0.9435269834753192</v>
       </c>
     </row>
     <row r="130">
@@ -14404,13 +14364,13 @@
         <v>3.2438</v>
       </c>
       <c r="AA130" t="n">
-        <v>0.3595775791169871</v>
+        <v>0.3595775791169893</v>
       </c>
       <c r="AB130" t="n">
-        <v>-0.2928715533741948</v>
+        <v>-0.2928715533741966</v>
       </c>
       <c r="AC130" t="n">
-        <v>-1.270749750504336</v>
+        <v>-1.270749750504335</v>
       </c>
     </row>
     <row r="131">
@@ -14511,13 +14471,13 @@
         <v>3.0048</v>
       </c>
       <c r="AA131" t="n">
-        <v>0.01869163592376171</v>
+        <v>0.01869163592376347</v>
       </c>
       <c r="AB131" t="n">
         <v>-2.030301789083663</v>
       </c>
       <c r="AC131" t="n">
-        <v>0.3448422268950473</v>
+        <v>0.3448422268950541</v>
       </c>
     </row>
     <row r="132">
@@ -14618,13 +14578,13 @@
         <v>3.0767</v>
       </c>
       <c r="AA132" t="n">
-        <v>-0.5744339805445581</v>
+        <v>-0.5744339805445546</v>
       </c>
       <c r="AB132" t="n">
-        <v>-0.01178974697390877</v>
+        <v>-0.01178974697390604</v>
       </c>
       <c r="AC132" t="n">
-        <v>1.472851612588326</v>
+        <v>1.472851612588327</v>
       </c>
     </row>
     <row r="133">
@@ -14728,10 +14688,10 @@
         <v>1.821707676364807</v>
       </c>
       <c r="AB133" t="n">
-        <v>1.116021677707036</v>
+        <v>1.116021677707038</v>
       </c>
       <c r="AC133" t="n">
-        <v>1.000478995159773</v>
+        <v>1.000478995159771</v>
       </c>
     </row>
     <row r="134">
@@ -14832,13 +14792,13 @@
         <v>3.733</v>
       </c>
       <c r="AA134" t="n">
-        <v>0.1332867446510078</v>
+        <v>0.1332867446510107</v>
       </c>
       <c r="AB134" t="n">
-        <v>-0.7341184714156076</v>
+        <v>-0.7341184714156102</v>
       </c>
       <c r="AC134" t="n">
-        <v>-1.448770793635815</v>
+        <v>-1.448770793635813</v>
       </c>
     </row>
     <row r="135">
@@ -14939,13 +14899,13 @@
         <v>3.0683</v>
       </c>
       <c r="AA135" t="n">
-        <v>-1.960366007524628</v>
+        <v>-1.960366007524627</v>
       </c>
       <c r="AB135" t="n">
-        <v>0.07680747324115039</v>
+        <v>0.07680747324115177</v>
       </c>
       <c r="AC135" t="n">
-        <v>0.1962329127012689</v>
+        <v>0.1962329127012684</v>
       </c>
     </row>
     <row r="136">
@@ -15049,10 +15009,10 @@
         <v>-1.167633181826518</v>
       </c>
       <c r="AB136" t="n">
-        <v>0.5779751942611173</v>
+        <v>0.5779751942611188</v>
       </c>
       <c r="AC136" t="n">
-        <v>0.7487451821044681</v>
+        <v>0.7487451821044668</v>
       </c>
     </row>
     <row r="137">
@@ -15153,13 +15113,13 @@
         <v>3.3515</v>
       </c>
       <c r="AA137" t="n">
-        <v>0.4138155751581711</v>
+        <v>0.4138155751581734</v>
       </c>
       <c r="AB137" t="n">
-        <v>0.4198271055396969</v>
+        <v>0.4198271055396975</v>
       </c>
       <c r="AC137" t="n">
-        <v>0.04282629869694119</v>
+        <v>0.04282629869693872</v>
       </c>
     </row>
     <row r="138">
@@ -15260,13 +15220,13 @@
         <v>3.7227</v>
       </c>
       <c r="AA138" t="n">
-        <v>0.07680451573380907</v>
+        <v>0.07680451573380724</v>
       </c>
       <c r="AB138" t="n">
-        <v>2.265060916631227</v>
+        <v>2.265060916631226</v>
       </c>
       <c r="AC138" t="n">
-        <v>-0.2143460194810888</v>
+        <v>-0.2143460194810919</v>
       </c>
     </row>
     <row r="139">
@@ -15367,13 +15327,13 @@
         <v>4.852</v>
       </c>
       <c r="AA139" t="n">
-        <v>2.17947362913291</v>
+        <v>2.179473629132909</v>
       </c>
       <c r="AB139" t="n">
-        <v>-1.273623277199197</v>
+        <v>-1.2736232771992</v>
       </c>
       <c r="AC139" t="n">
-        <v>-2.453114485013544</v>
+        <v>-2.453114485013541</v>
       </c>
     </row>
     <row r="140">
@@ -15477,10 +15437,10 @@
         <v>-2.15056788651843</v>
       </c>
       <c r="AB140" t="n">
-        <v>0.2622899626488743</v>
+        <v>0.2622899626488727</v>
       </c>
       <c r="AC140" t="n">
-        <v>0.09966226630260443</v>
+        <v>0.09966226630260537</v>
       </c>
     </row>
     <row r="141">
@@ -15581,13 +15541,13 @@
         <v>3.2151</v>
       </c>
       <c r="AA141" t="n">
-        <v>0.1496237485970303</v>
+        <v>0.1496237485970298</v>
       </c>
       <c r="AB141" t="n">
-        <v>-0.8209041852927774</v>
+        <v>-0.8209041852927822</v>
       </c>
       <c r="AC141" t="n">
-        <v>-1.657356670966181</v>
+        <v>-1.657356670966179</v>
       </c>
     </row>
     <row r="142">
@@ -15688,13 +15648,13 @@
         <v>4.6117</v>
       </c>
       <c r="AA142" t="n">
-        <v>-0.05553135167493665</v>
+        <v>-0.05553135167493559</v>
       </c>
       <c r="AB142" t="n">
-        <v>2.117699225796308</v>
+        <v>2.117699225796307</v>
       </c>
       <c r="AC142" t="n">
-        <v>0.6559806862345796</v>
+        <v>0.6559806862345792</v>
       </c>
     </row>
     <row r="143">
@@ -15795,13 +15755,13 @@
         <v>3.1459</v>
       </c>
       <c r="AA143" t="n">
-        <v>1.138930303484736</v>
+        <v>1.138930303484734</v>
       </c>
       <c r="AB143" t="n">
-        <v>0.4627160689456399</v>
+        <v>0.46271606894564</v>
       </c>
       <c r="AC143" t="n">
-        <v>-0.7614426658941675</v>
+        <v>-0.7614426658941715</v>
       </c>
     </row>
     <row r="144">
@@ -15902,13 +15862,13 @@
         <v>3.7604</v>
       </c>
       <c r="AA144" t="n">
-        <v>-0.4971777181913087</v>
+        <v>-0.4971777181913096</v>
       </c>
       <c r="AB144" t="n">
-        <v>0.4308715232204568</v>
+        <v>0.4308715232204555</v>
       </c>
       <c r="AC144" t="n">
-        <v>0.8617759688974355</v>
+        <v>0.8617759688974372</v>
       </c>
     </row>
     <row r="145">
@@ -16009,13 +15969,13 @@
         <v>3.5711</v>
       </c>
       <c r="AA145" t="n">
-        <v>0.5857907896313518</v>
+        <v>0.5857907896313522</v>
       </c>
       <c r="AB145" t="n">
-        <v>-1.762326758941407</v>
+        <v>-1.762326758941405</v>
       </c>
       <c r="AC145" t="n">
-        <v>-0.8152363323978427</v>
+        <v>-0.8152363323978417</v>
       </c>
     </row>
     <row r="146">
@@ -16116,13 +16076,13 @@
         <v>2.8629</v>
       </c>
       <c r="AA146" t="n">
-        <v>-1.959716141035034</v>
+        <v>-1.959716141035032</v>
       </c>
       <c r="AB146" t="n">
-        <v>0.1959137727568256</v>
+        <v>0.1959137727568271</v>
       </c>
       <c r="AC146" t="n">
-        <v>0.211372408152443</v>
+        <v>0.2113724081524411</v>
       </c>
     </row>
     <row r="147">
@@ -16223,13 +16183,13 @@
         <v>3.8543</v>
       </c>
       <c r="AA147" t="n">
-        <v>0.7201067645798651</v>
+        <v>0.7201067645798664</v>
       </c>
       <c r="AB147" t="n">
-        <v>0.4680535248906204</v>
+        <v>0.4680535248906224</v>
       </c>
       <c r="AC147" t="n">
-        <v>1.000206351347875</v>
+        <v>1.000206351347877</v>
       </c>
     </row>
     <row r="148">
@@ -16330,10 +16290,10 @@
         <v>4.1666</v>
       </c>
       <c r="AA148" t="n">
-        <v>1.232463704447488</v>
+        <v>1.23246370444749</v>
       </c>
       <c r="AB148" t="n">
-        <v>-1.334319438392517</v>
+        <v>-1.334319438392512</v>
       </c>
       <c r="AC148" t="n">
         <v>1.872477956804842</v>
@@ -16437,13 +16397,13 @@
         <v>3.3529</v>
       </c>
       <c r="AA149" t="n">
-        <v>1.246555817646276</v>
+        <v>1.246555817646274</v>
       </c>
       <c r="AB149" t="n">
-        <v>0.01546277967363296</v>
+        <v>0.01546277967363392</v>
       </c>
       <c r="AC149" t="n">
-        <v>-0.4345889390887268</v>
+        <v>-0.4345889390887299</v>
       </c>
     </row>
     <row r="150">
@@ -16544,13 +16504,13 @@
         <v>3.142</v>
       </c>
       <c r="AA150" t="n">
-        <v>0.5713918512611597</v>
+        <v>0.5713918512611604</v>
       </c>
       <c r="AB150" t="n">
-        <v>-0.1975662252919681</v>
+        <v>-0.1975662252919673</v>
       </c>
       <c r="AC150" t="n">
-        <v>-0.1931161576934171</v>
+        <v>-0.1931161576934201</v>
       </c>
     </row>
     <row r="151">
@@ -16651,13 +16611,13 @@
         <v>5.6475</v>
       </c>
       <c r="AA151" t="n">
-        <v>3.722701551857204</v>
+        <v>3.722701551857203</v>
       </c>
       <c r="AB151" t="n">
-        <v>-1.43999268900987</v>
+        <v>-1.439992689009868</v>
       </c>
       <c r="AC151" t="n">
-        <v>-0.03829137482476021</v>
+        <v>-0.03829137482475755</v>
       </c>
     </row>
     <row r="152">
@@ -16758,13 +16718,13 @@
         <v>4.1813</v>
       </c>
       <c r="AA152" t="n">
-        <v>-0.08122271137598684</v>
+        <v>-0.08122271137598756</v>
       </c>
       <c r="AB152" t="n">
-        <v>-0.05108800216959496</v>
+        <v>-0.05108800216959412</v>
       </c>
       <c r="AC152" t="n">
-        <v>1.69526897452462</v>
+        <v>1.695268974524622</v>
       </c>
     </row>
     <row r="153">
@@ -16865,13 +16825,13 @@
         <v>3.3673</v>
       </c>
       <c r="AA153" t="n">
-        <v>0.106783032880423</v>
+        <v>0.1067830328804229</v>
       </c>
       <c r="AB153" t="n">
-        <v>0.9197018625713195</v>
+        <v>0.9197018625713199</v>
       </c>
       <c r="AC153" t="n">
-        <v>0.9222333547097298</v>
+        <v>0.9222333547097306</v>
       </c>
     </row>
     <row r="154">
@@ -16972,13 +16932,13 @@
         <v>3.5954</v>
       </c>
       <c r="AA154" t="n">
-        <v>0.5326584537925223</v>
+        <v>0.5326584537925222</v>
       </c>
       <c r="AB154" t="n">
         <v>-1.790845051485749</v>
       </c>
       <c r="AC154" t="n">
-        <v>-0.3292401364332263</v>
+        <v>-0.3292401364332259</v>
       </c>
     </row>
     <row r="155">
@@ -17079,13 +17039,13 @@
         <v>3.208</v>
       </c>
       <c r="AA155" t="n">
-        <v>0.08274639081059353</v>
+        <v>0.08274639081059486</v>
       </c>
       <c r="AB155" t="n">
-        <v>-0.7274710728691588</v>
+        <v>-0.7274710728691564</v>
       </c>
       <c r="AC155" t="n">
-        <v>0.8059192353137267</v>
+        <v>0.8059192353137266</v>
       </c>
     </row>
     <row r="156">
@@ -17189,10 +17149,10 @@
         <v>4.637390816843109</v>
       </c>
       <c r="AB156" t="n">
-        <v>-2.566613601941325</v>
+        <v>-2.566613601941321</v>
       </c>
       <c r="AC156" t="n">
-        <v>0.6496289269854498</v>
+        <v>0.649628926985454</v>
       </c>
     </row>
     <row r="157">
@@ -17293,13 +17253,13 @@
         <v>3.0349</v>
       </c>
       <c r="AA157" t="n">
-        <v>-0.3542719348736636</v>
+        <v>-0.35427193487366</v>
       </c>
       <c r="AB157" t="n">
-        <v>0.5835941370409597</v>
+        <v>0.5835941370409615</v>
       </c>
       <c r="AC157" t="n">
-        <v>1.33655902564494</v>
+        <v>1.336559025644939</v>
       </c>
     </row>
     <row r="158">
@@ -17400,13 +17360,13 @@
         <v>3.4229</v>
       </c>
       <c r="AA158" t="n">
-        <v>-2.159208970914719</v>
+        <v>-2.159208970914715</v>
       </c>
       <c r="AB158" t="n">
-        <v>0.5224334942535043</v>
+        <v>0.5224334942535035</v>
       </c>
       <c r="AC158" t="n">
-        <v>-0.01782214140441809</v>
+        <v>-0.01782214140442036</v>
       </c>
     </row>
     <row r="159">
@@ -17507,13 +17467,13 @@
         <v>1.9824</v>
       </c>
       <c r="AA159" t="n">
-        <v>-1.952490891748482</v>
+        <v>-1.95249089174848</v>
       </c>
       <c r="AB159" t="n">
-        <v>0.3866990333831239</v>
+        <v>0.3866990333831234</v>
       </c>
       <c r="AC159" t="n">
-        <v>0.6500689135998361</v>
+        <v>0.6500689135998373</v>
       </c>
     </row>
     <row r="160">
@@ -17614,13 +17574,13 @@
         <v>2.8557</v>
       </c>
       <c r="AA160" t="n">
-        <v>-0.9889382885393651</v>
+        <v>-0.9889382885393617</v>
       </c>
       <c r="AB160" t="n">
-        <v>0.431358918623472</v>
+        <v>0.4313589186234742</v>
       </c>
       <c r="AC160" t="n">
-        <v>0.9775162887176033</v>
+        <v>0.9775162887176022</v>
       </c>
     </row>
     <row r="161">
@@ -17721,13 +17681,13 @@
         <v>2.8913</v>
       </c>
       <c r="AA161" t="n">
-        <v>-2.095262113775035</v>
+        <v>-2.095262113775033</v>
       </c>
       <c r="AB161" t="n">
-        <v>0.8413765366788963</v>
+        <v>0.841376536678896</v>
       </c>
       <c r="AC161" t="n">
-        <v>-0.3521407221318898</v>
+        <v>-0.352140722131891</v>
       </c>
     </row>
     <row r="162">
@@ -17828,13 +17788,13 @@
         <v>2.7144</v>
       </c>
       <c r="AA162" t="n">
-        <v>-1.238025892814028</v>
+        <v>-1.238025892814029</v>
       </c>
       <c r="AB162" t="n">
-        <v>0.6102461737667167</v>
+        <v>0.6102461737667149</v>
       </c>
       <c r="AC162" t="n">
-        <v>-0.9746059282778878</v>
+        <v>-0.9746059282778898</v>
       </c>
     </row>
     <row r="163">
@@ -17935,13 +17895,13 @@
         <v>3.0562</v>
       </c>
       <c r="AA163" t="n">
-        <v>-0.845820372096272</v>
+        <v>-0.8458203720962707</v>
       </c>
       <c r="AB163" t="n">
-        <v>0.539888549253027</v>
+        <v>0.5398885492530252</v>
       </c>
       <c r="AC163" t="n">
-        <v>-1.465628342338368</v>
+        <v>-1.465628342338372</v>
       </c>
     </row>
     <row r="164">
@@ -18042,13 +18002,13 @@
         <v>3.4213</v>
       </c>
       <c r="AA164" t="n">
-        <v>-0.5223144392522885</v>
+        <v>-0.5223144392522878</v>
       </c>
       <c r="AB164" t="n">
-        <v>-0.6786085748374698</v>
+        <v>-0.6786085748374687</v>
       </c>
       <c r="AC164" t="n">
-        <v>0.774951690927379</v>
+        <v>0.7749516909273845</v>
       </c>
     </row>
     <row r="165">
@@ -18149,13 +18109,13 @@
         <v>2.9073</v>
       </c>
       <c r="AA165" t="n">
-        <v>-0.05613962365084706</v>
+        <v>-0.05613962365084746</v>
       </c>
       <c r="AB165" t="n">
-        <v>-1.099249572603569</v>
+        <v>-1.099249572603571</v>
       </c>
       <c r="AC165" t="n">
-        <v>-0.8346515669397111</v>
+        <v>-0.8346515669397084</v>
       </c>
     </row>
     <row r="166">
@@ -18256,13 +18216,13 @@
         <v>2.9146</v>
       </c>
       <c r="AA166" t="n">
-        <v>0.9155004238818683</v>
+        <v>0.9155004238818666</v>
       </c>
       <c r="AB166" t="n">
-        <v>0.6036736137403246</v>
+        <v>0.6036736137403238</v>
       </c>
       <c r="AC166" t="n">
-        <v>-0.5961658678931205</v>
+        <v>-0.5961658678931225</v>
       </c>
     </row>
     <row r="167">
@@ -18366,10 +18326,10 @@
         <v>-1.074221761234297</v>
       </c>
       <c r="AB167" t="n">
-        <v>-1.866372648095286</v>
+        <v>-1.866372648095288</v>
       </c>
       <c r="AC167" t="n">
-        <v>-1.06253998224268</v>
+        <v>-1.062539982242674</v>
       </c>
     </row>
     <row r="168">
@@ -18470,13 +18430,13 @@
         <v>4.046</v>
       </c>
       <c r="AA168" t="n">
-        <v>0.4967762637286869</v>
+        <v>0.4967762637286902</v>
       </c>
       <c r="AB168" t="n">
         <v>-1.645112956622861</v>
       </c>
       <c r="AC168" t="n">
-        <v>-0.6752468471526789</v>
+        <v>-0.6752468471526748</v>
       </c>
     </row>
     <row r="169">
@@ -18580,10 +18540,10 @@
         <v>-2.321489052262239</v>
       </c>
       <c r="AB169" t="n">
-        <v>-0.4816341389119768</v>
+        <v>-0.4816341389119781</v>
       </c>
       <c r="AC169" t="n">
-        <v>0.0922301239871529</v>
+        <v>0.09223012398715473</v>
       </c>
     </row>
     <row r="170">
@@ -18684,13 +18644,13 @@
         <v>2.3958</v>
       </c>
       <c r="AA170" t="n">
-        <v>-1.907474686840304</v>
+        <v>-1.9074746868403</v>
       </c>
       <c r="AB170" t="n">
-        <v>-0.8362051218063806</v>
+        <v>-0.8362051218063802</v>
       </c>
       <c r="AC170" t="n">
-        <v>0.2458553896200409</v>
+        <v>0.2458553896200412</v>
       </c>
     </row>
     <row r="171">
@@ -18791,13 +18751,13 @@
         <v>2.7535</v>
       </c>
       <c r="AA171" t="n">
-        <v>-0.6517078751140181</v>
+        <v>-0.65170787511402</v>
       </c>
       <c r="AB171" t="n">
-        <v>-0.2462380873654319</v>
+        <v>-0.2462380873654347</v>
       </c>
       <c r="AC171" t="n">
-        <v>-1.511527448646886</v>
+        <v>-1.511527448646887</v>
       </c>
     </row>
     <row r="172">
@@ -18898,13 +18858,13 @@
         <v>4.0483</v>
       </c>
       <c r="AA172" t="n">
-        <v>1.053496759435326</v>
+        <v>1.053496759435328</v>
       </c>
       <c r="AB172" t="n">
-        <v>-1.750987537103764</v>
+        <v>-1.750987537103763</v>
       </c>
       <c r="AC172" t="n">
-        <v>0.1503539336395621</v>
+        <v>0.1503539336395623</v>
       </c>
     </row>
     <row r="173">
@@ -19005,13 +18965,13 @@
         <v>2.9511</v>
       </c>
       <c r="AA173" t="n">
-        <v>-2.151566487211571</v>
+        <v>-2.151566487211569</v>
       </c>
       <c r="AB173" t="n">
-        <v>-0.4530820739440483</v>
+        <v>-0.4530820739440504</v>
       </c>
       <c r="AC173" t="n">
-        <v>-0.3079415686079625</v>
+        <v>-0.3079415686079616</v>
       </c>
     </row>
     <row r="174">
@@ -19112,10 +19072,10 @@
         <v>4.4293</v>
       </c>
       <c r="AA174" t="n">
-        <v>1.825879018106961</v>
+        <v>1.82587901810696</v>
       </c>
       <c r="AB174" t="n">
-        <v>-1.311593153129717</v>
+        <v>-1.311593153129712</v>
       </c>
       <c r="AC174" t="n">
         <v>1.424275037691393</v>
@@ -19219,13 +19179,13 @@
         <v>4.6626</v>
       </c>
       <c r="AA175" t="n">
-        <v>2.786351078947571</v>
+        <v>2.786351078947569</v>
       </c>
       <c r="AB175" t="n">
-        <v>1.00056391903541</v>
+        <v>1.000563919035412</v>
       </c>
       <c r="AC175" t="n">
-        <v>0.3946700081574133</v>
+        <v>0.3946700081574122</v>
       </c>
     </row>
     <row r="176">
@@ -19326,13 +19286,13 @@
         <v>3.4623</v>
       </c>
       <c r="AA176" t="n">
-        <v>-1.508423736836538</v>
+        <v>-1.50842373683654</v>
       </c>
       <c r="AB176" t="n">
         <v>1.566999837571913</v>
       </c>
       <c r="AC176" t="n">
-        <v>0.8090493238503538</v>
+        <v>0.8090493238503512</v>
       </c>
     </row>
     <row r="177">
@@ -19433,13 +19393,13 @@
         <v>3.2717</v>
       </c>
       <c r="AA177" t="n">
-        <v>0.3818185988988928</v>
+        <v>0.381818598898892</v>
       </c>
       <c r="AB177" t="n">
-        <v>1.199267327716355</v>
+        <v>1.199267327716354</v>
       </c>
       <c r="AC177" t="n">
-        <v>-0.8880049039255393</v>
+        <v>-0.8880049039255419</v>
       </c>
     </row>
     <row r="178">
@@ -19540,13 +19500,13 @@
         <v>4.1472</v>
       </c>
       <c r="AA178" t="n">
-        <v>0.5841879494207926</v>
+        <v>0.5841879494207908</v>
       </c>
       <c r="AB178" t="n">
-        <v>0.4395921374536788</v>
+        <v>0.4395921374536744</v>
       </c>
       <c r="AC178" t="n">
-        <v>-2.108413406251946</v>
+        <v>-2.108413406251945</v>
       </c>
     </row>
     <row r="179">
@@ -19647,13 +19607,13 @@
         <v>3.6648</v>
       </c>
       <c r="AA179" t="n">
-        <v>-1.444354944160785</v>
+        <v>-1.444354944160781</v>
       </c>
       <c r="AB179" t="n">
-        <v>-1.794742480263267</v>
+        <v>-1.794742480263266</v>
       </c>
       <c r="AC179" t="n">
-        <v>1.367785372189645</v>
+        <v>1.367785372189648</v>
       </c>
     </row>
     <row r="180">
@@ -19754,13 +19714,13 @@
         <v>3.3884</v>
       </c>
       <c r="AA180" t="n">
-        <v>1.367599497942281</v>
+        <v>1.367599497942282</v>
       </c>
       <c r="AB180" t="n">
-        <v>0.3911495345745403</v>
+        <v>0.3911495345745379</v>
       </c>
       <c r="AC180" t="n">
-        <v>-1.015822509032123</v>
+        <v>-1.015822509032122</v>
       </c>
     </row>
     <row r="181">
@@ -19861,13 +19821,13 @@
         <v>3.6971</v>
       </c>
       <c r="AA181" t="n">
-        <v>0.7396325806989681</v>
+        <v>0.739632580698968</v>
       </c>
       <c r="AB181" t="n">
-        <v>-0.1398299309835499</v>
+        <v>-0.1398299309835492</v>
       </c>
       <c r="AC181" t="n">
-        <v>0.6765025266464637</v>
+        <v>0.6765025266464683</v>
       </c>
     </row>
     <row r="182">
@@ -19968,13 +19928,13 @@
         <v>2.2809</v>
       </c>
       <c r="AA182" t="n">
-        <v>-0.924206750066232</v>
+        <v>-0.9242067500662305</v>
       </c>
       <c r="AB182" t="n">
-        <v>-0.946497013466996</v>
+        <v>-0.9464970134669968</v>
       </c>
       <c r="AC182" t="n">
-        <v>0.4893375467800716</v>
+        <v>0.4893375467800752</v>
       </c>
     </row>
     <row r="183">
@@ -20078,10 +20038,10 @@
         <v>0.8658544392348685</v>
       </c>
       <c r="AB183" t="n">
-        <v>-2.119676755180424</v>
+        <v>-2.119676755180426</v>
       </c>
       <c r="AC183" t="n">
-        <v>-2.782897792174143</v>
+        <v>-2.782897792174142</v>
       </c>
     </row>
     <row r="184">
@@ -20182,13 +20142,13 @@
         <v>2.8164</v>
       </c>
       <c r="AA184" t="n">
-        <v>-0.2830623260348086</v>
+        <v>-0.2830623260348088</v>
       </c>
       <c r="AB184" t="n">
-        <v>1.438854656907009</v>
+        <v>1.438854656907011</v>
       </c>
       <c r="AC184" t="n">
-        <v>1.152874233877011</v>
+        <v>1.152874233877009</v>
       </c>
     </row>
     <row r="185">
@@ -20289,13 +20249,13 @@
         <v>2.614</v>
       </c>
       <c r="AA185" t="n">
-        <v>-1.533928546658228</v>
+        <v>-1.533928546658226</v>
       </c>
       <c r="AB185" t="n">
-        <v>-0.5373055530873936</v>
+        <v>-0.537305553087394</v>
       </c>
       <c r="AC185" t="n">
-        <v>0.1222615664015889</v>
+        <v>0.1222615664015882</v>
       </c>
     </row>
     <row r="186">
@@ -20396,13 +20356,13 @@
         <v>4.0111</v>
       </c>
       <c r="AA186" t="n">
-        <v>-1.02791151303287</v>
+        <v>-1.027911513032867</v>
       </c>
       <c r="AB186" t="n">
-        <v>-2.553266130690132</v>
+        <v>-2.55326613069013</v>
       </c>
       <c r="AC186" t="n">
-        <v>1.039969139657715</v>
+        <v>1.039969139657719</v>
       </c>
     </row>
     <row r="187">
@@ -20503,13 +20463,13 @@
         <v>2.2317</v>
       </c>
       <c r="AA187" t="n">
-        <v>-0.4881506781996749</v>
+        <v>-0.4881506781996758</v>
       </c>
       <c r="AB187" t="n">
-        <v>-0.005625365941628678</v>
+        <v>-0.005625365941632332</v>
       </c>
       <c r="AC187" t="n">
-        <v>-0.9508265662251305</v>
+        <v>-0.9508265662251301</v>
       </c>
     </row>
     <row r="188">
@@ -20610,13 +20570,13 @@
         <v>2.5565</v>
       </c>
       <c r="AA188" t="n">
-        <v>-0.7856247252449113</v>
+        <v>-0.7856247252449111</v>
       </c>
       <c r="AB188" t="n">
-        <v>0.2364612745279224</v>
+        <v>0.2364612745279219</v>
       </c>
       <c r="AC188" t="n">
-        <v>-1.121538914124308</v>
+        <v>-1.121538914124309</v>
       </c>
     </row>
     <row r="189">
@@ -20717,13 +20677,13 @@
         <v>4.7112</v>
       </c>
       <c r="AA189" t="n">
-        <v>1.109315159659334</v>
+        <v>1.109315159659332</v>
       </c>
       <c r="AB189" t="n">
-        <v>-2.584939610125182</v>
+        <v>-2.584939610125184</v>
       </c>
       <c r="AC189" t="n">
-        <v>-2.230015997151162</v>
+        <v>-2.230015997151158</v>
       </c>
     </row>
     <row r="190">
@@ -20824,10 +20784,10 @@
         <v>3.9758</v>
       </c>
       <c r="AA190" t="n">
-        <v>0.9515424736884384</v>
+        <v>0.9515424736884404</v>
       </c>
       <c r="AB190" t="n">
-        <v>-0.4568774212324657</v>
+        <v>-0.4568774212324613</v>
       </c>
       <c r="AC190" t="n">
         <v>1.657161685626332</v>
@@ -20931,13 +20891,13 @@
         <v>3.6577</v>
       </c>
       <c r="AA191" t="n">
-        <v>1.215824595973368</v>
+        <v>1.215824595973365</v>
       </c>
       <c r="AB191" t="n">
-        <v>2.103962758253138</v>
+        <v>2.103962758253136</v>
       </c>
       <c r="AC191" t="n">
-        <v>-0.7316513186774281</v>
+        <v>-0.7316513186774319</v>
       </c>
     </row>
     <row r="192">
@@ -21038,10 +20998,10 @@
         <v>4.5034</v>
       </c>
       <c r="AA192" t="n">
-        <v>2.123768155247364</v>
+        <v>2.123768155247365</v>
       </c>
       <c r="AB192" t="n">
-        <v>0.2513695968607749</v>
+        <v>0.2513695968607781</v>
       </c>
       <c r="AC192" t="n">
         <v>1.452226928808716</v>
@@ -21145,13 +21105,13 @@
         <v>4.9364</v>
       </c>
       <c r="AA193" t="n">
-        <v>0.7865226449092522</v>
+        <v>0.7865226449092571</v>
       </c>
       <c r="AB193" t="n">
-        <v>-3.944604934631364</v>
+        <v>-3.944604934631363</v>
       </c>
       <c r="AC193" t="n">
-        <v>-0.3692627025226625</v>
+        <v>-0.3692627025226556</v>
       </c>
     </row>
     <row r="194">
@@ -21252,13 +21212,13 @@
         <v>2.8802</v>
       </c>
       <c r="AA194" t="n">
-        <v>0.2055495980185058</v>
+        <v>0.2055495980185043</v>
       </c>
       <c r="AB194" t="n">
-        <v>0.04331740314736136</v>
+        <v>0.04331740314735838</v>
       </c>
       <c r="AC194" t="n">
-        <v>-1.17356257440888</v>
+        <v>-1.173562574408882</v>
       </c>
     </row>
     <row r="195">
@@ -21359,13 +21319,13 @@
         <v>3.4473</v>
       </c>
       <c r="AA195" t="n">
-        <v>0.7508813970011774</v>
+        <v>0.7508813970011772</v>
       </c>
       <c r="AB195" t="n">
-        <v>0.5020721152219457</v>
+        <v>0.5020721152219459</v>
       </c>
       <c r="AC195" t="n">
-        <v>-0.0299074890020812</v>
+        <v>-0.0299074890020825</v>
       </c>
     </row>
     <row r="196">
@@ -21466,13 +21426,13 @@
         <v>2.4147</v>
       </c>
       <c r="AA196" t="n">
-        <v>-0.3193354758686331</v>
+        <v>-0.3193354758686336</v>
       </c>
       <c r="AB196" t="n">
-        <v>-0.7842358012132606</v>
+        <v>-0.7842358012132619</v>
       </c>
       <c r="AC196" t="n">
-        <v>-1.097596161974796</v>
+        <v>-1.097596161974797</v>
       </c>
     </row>
     <row r="197">
@@ -21573,13 +21533,13 @@
         <v>3.8165</v>
       </c>
       <c r="AA197" t="n">
-        <v>-0.04893293217070986</v>
+        <v>-0.04893293217070902</v>
       </c>
       <c r="AB197" t="n">
-        <v>-0.2391665795071746</v>
+        <v>-0.239166579507174</v>
       </c>
       <c r="AC197" t="n">
-        <v>0.9495584728759168</v>
+        <v>0.9495584728759165</v>
       </c>
     </row>
     <row r="198">
@@ -21680,13 +21640,13 @@
         <v>3.2267</v>
       </c>
       <c r="AA198" t="n">
-        <v>1.480120192641615</v>
+        <v>1.480120192641614</v>
       </c>
       <c r="AB198" t="n">
-        <v>0.625268419194398</v>
+        <v>0.6252684191943977</v>
       </c>
       <c r="AC198" t="n">
-        <v>-0.04496617016873554</v>
+        <v>-0.0449661701687372</v>
       </c>
     </row>
     <row r="199">
@@ -21787,13 +21747,13 @@
         <v>4.0742</v>
       </c>
       <c r="AA199" t="n">
-        <v>2.55104430539018</v>
+        <v>2.551044305390179</v>
       </c>
       <c r="AB199" t="n">
-        <v>0.07901963294349394</v>
+        <v>0.0790196329434959</v>
       </c>
       <c r="AC199" t="n">
-        <v>0.4157946681251669</v>
+        <v>0.415794668125166</v>
       </c>
     </row>
     <row r="200">
@@ -21894,13 +21854,13 @@
         <v>3.2454</v>
       </c>
       <c r="AA200" t="n">
-        <v>1.034956569148255</v>
+        <v>1.034956569148254</v>
       </c>
       <c r="AB200" t="n">
         <v>-0.8458436672070425</v>
       </c>
       <c r="AC200" t="n">
-        <v>-0.9249856782106549</v>
+        <v>-0.9249856782106538</v>
       </c>
     </row>
     <row r="201">
@@ -22001,13 +21961,13 @@
         <v>2.7248</v>
       </c>
       <c r="AA201" t="n">
-        <v>0.8614119433795276</v>
+        <v>0.8614119433795283</v>
       </c>
       <c r="AB201" t="n">
-        <v>0.1224353006160167</v>
+        <v>0.1224353006160169</v>
       </c>
       <c r="AC201" t="n">
-        <v>-0.2198988424326972</v>
+        <v>-0.2198988424326976</v>
       </c>
     </row>
     <row r="202">
@@ -22108,13 +22068,13 @@
         <v>4.6239</v>
       </c>
       <c r="AA202" t="n">
-        <v>2.096689337987652</v>
+        <v>2.096689337987649</v>
       </c>
       <c r="AB202" t="n">
-        <v>1.806121325051679</v>
+        <v>1.806121325051674</v>
       </c>
       <c r="AC202" t="n">
-        <v>-2.14663676023648</v>
+        <v>-2.146636760236483</v>
       </c>
     </row>
     <row r="203">
@@ -22215,13 +22175,13 @@
         <v>4.6126</v>
       </c>
       <c r="AA203" t="n">
-        <v>-0.04438382698731939</v>
+        <v>-0.04438382698731778</v>
       </c>
       <c r="AB203" t="n">
-        <v>-1.9054797407376</v>
+        <v>-1.905479740737596</v>
       </c>
       <c r="AC203" t="n">
-        <v>1.916423686472605</v>
+        <v>1.916423686472608</v>
       </c>
     </row>
     <row r="204">
@@ -22322,13 +22282,13 @@
         <v>4.4003</v>
       </c>
       <c r="AA204" t="n">
-        <v>-0.3155566332640631</v>
+        <v>-0.3155566332640663</v>
       </c>
       <c r="AB204" t="n">
         <v>2.834366538618307</v>
       </c>
       <c r="AC204" t="n">
-        <v>1.40451800021745</v>
+        <v>1.404518000217449</v>
       </c>
     </row>
     <row r="205">
@@ -22429,13 +22389,13 @@
         <v>3.5278</v>
       </c>
       <c r="AA205" t="n">
-        <v>-0.1751633145828798</v>
+        <v>-0.1751633145828782</v>
       </c>
       <c r="AB205" t="n">
-        <v>1.475861241840274</v>
+        <v>1.475861241840276</v>
       </c>
       <c r="AC205" t="n">
-        <v>1.417296380100567</v>
+        <v>1.417296380100566</v>
       </c>
     </row>
     <row r="206">
@@ -22536,13 +22496,13 @@
         <v>3.019</v>
       </c>
       <c r="AA206" t="n">
-        <v>-0.182841025761391</v>
+        <v>-0.1828410257613932</v>
       </c>
       <c r="AB206" t="n">
         <v>1.415784239427915</v>
       </c>
       <c r="AC206" t="n">
-        <v>0.6900943007575685</v>
+        <v>0.6900943007575691</v>
       </c>
     </row>
     <row r="207">
@@ -22646,10 +22606,10 @@
         <v>1.105102345470378</v>
       </c>
       <c r="AB207" t="n">
-        <v>1.839116896573163</v>
+        <v>1.839116896573166</v>
       </c>
       <c r="AC207" t="n">
-        <v>1.447000368558249</v>
+        <v>1.447000368558244</v>
       </c>
     </row>
     <row r="208">
@@ -22750,13 +22710,13 @@
         <v>2.5417</v>
       </c>
       <c r="AA208" t="n">
-        <v>-0.5767398046381124</v>
+        <v>-0.5767398046381135</v>
       </c>
       <c r="AB208" t="n">
-        <v>-0.7104552997047103</v>
+        <v>-0.7104552997047145</v>
       </c>
       <c r="AC208" t="n">
-        <v>-1.238685480494962</v>
+        <v>-1.23868548049496</v>
       </c>
     </row>
     <row r="209">
@@ -22857,13 +22817,13 @@
         <v>4.625</v>
       </c>
       <c r="AA209" t="n">
-        <v>0.8548337116807145</v>
+        <v>0.8548337116807161</v>
       </c>
       <c r="AB209" t="n">
-        <v>-2.031076154736445</v>
+        <v>-2.031076154736439</v>
       </c>
       <c r="AC209" t="n">
-        <v>1.768257472651361</v>
+        <v>1.768257472651364</v>
       </c>
     </row>
     <row r="210">
@@ -22967,10 +22927,10 @@
         <v>2.674566558319762</v>
       </c>
       <c r="AB210" t="n">
-        <v>0.7918979620333746</v>
+        <v>0.791897962033374</v>
       </c>
       <c r="AC210" t="n">
-        <v>-0.1659004476833399</v>
+        <v>-0.1659004476833405</v>
       </c>
     </row>
     <row r="211">
@@ -23071,13 +23031,13 @@
         <v>2.1893</v>
       </c>
       <c r="AA211" t="n">
-        <v>-1.97179909377381</v>
+        <v>-1.971799093773809</v>
       </c>
       <c r="AB211" t="n">
-        <v>0.2187837958731146</v>
+        <v>0.2187837958731135</v>
       </c>
       <c r="AC211" t="n">
-        <v>-0.2332304495049665</v>
+        <v>-0.2332304495049688</v>
       </c>
     </row>
     <row r="212">
@@ -23178,13 +23138,13 @@
         <v>4.9977</v>
       </c>
       <c r="AA212" t="n">
-        <v>1.216715847370835</v>
+        <v>1.216715847370836</v>
       </c>
       <c r="AB212" t="n">
-        <v>-2.134768527207632</v>
+        <v>-2.134768527207627</v>
       </c>
       <c r="AC212" t="n">
-        <v>2.570556810541357</v>
+        <v>2.570556810541365</v>
       </c>
     </row>
     <row r="213">
@@ -23285,13 +23245,13 @@
         <v>4.6479</v>
       </c>
       <c r="AA213" t="n">
-        <v>2.560572893000826</v>
+        <v>2.560572893000823</v>
       </c>
       <c r="AB213" t="n">
-        <v>1.521340653894786</v>
+        <v>1.521340653894788</v>
       </c>
       <c r="AC213" t="n">
-        <v>1.007343155200135</v>
+        <v>1.007343155200132</v>
       </c>
     </row>
     <row r="214">
@@ -23392,13 +23352,13 @@
         <v>3.1819</v>
       </c>
       <c r="AA214" t="n">
-        <v>0.4790211656100519</v>
+        <v>0.4790211656100504</v>
       </c>
       <c r="AB214" t="n">
-        <v>1.099971261367319</v>
+        <v>1.099971261367322</v>
       </c>
       <c r="AC214" t="n">
-        <v>0.7094637420148855</v>
+        <v>0.7094637420148823</v>
       </c>
     </row>
     <row r="215">
@@ -23505,7 +23465,7 @@
         <v>0.2977916269510855</v>
       </c>
       <c r="AC215" t="n">
-        <v>0.07616563608976055</v>
+        <v>0.07616563608975906</v>
       </c>
     </row>
     <row r="216">
@@ -23606,13 +23566,13 @@
         <v>3.0678</v>
       </c>
       <c r="AA216" t="n">
-        <v>-1.039621324394168</v>
+        <v>-1.039621324394166</v>
       </c>
       <c r="AB216" t="n">
-        <v>-0.3442721767073547</v>
+        <v>-0.3442721767073556</v>
       </c>
       <c r="AC216" t="n">
-        <v>0.403965878366464</v>
+        <v>0.4039658783664669</v>
       </c>
     </row>
     <row r="217">
@@ -23713,13 +23673,13 @@
         <v>2.8994</v>
       </c>
       <c r="AA217" t="n">
-        <v>0.01961955254359278</v>
+        <v>0.01961955254359415</v>
       </c>
       <c r="AB217" t="n">
-        <v>-0.3204004836296685</v>
+        <v>-0.3204004836296717</v>
       </c>
       <c r="AC217" t="n">
-        <v>-1.815923645925487</v>
+        <v>-1.815923645925489</v>
       </c>
     </row>
     <row r="218">
@@ -23820,13 +23780,13 @@
         <v>3.2565</v>
       </c>
       <c r="AA218" t="n">
-        <v>0.8839584544960778</v>
+        <v>0.8839584544960738</v>
       </c>
       <c r="AB218" t="n">
-        <v>0.6497917094825847</v>
+        <v>0.6497917094825832</v>
       </c>
       <c r="AC218" t="n">
-        <v>-0.7367439417983829</v>
+        <v>-0.7367439417983834</v>
       </c>
     </row>
     <row r="219">
@@ -23927,13 +23887,13 @@
         <v>3.1036</v>
       </c>
       <c r="AA219" t="n">
-        <v>-1.918092926888721</v>
+        <v>-1.918092926888719</v>
       </c>
       <c r="AB219" t="n">
-        <v>-0.08103788384715707</v>
+        <v>-0.08103788384715903</v>
       </c>
       <c r="AC219" t="n">
-        <v>-0.8640310737524184</v>
+        <v>-0.8640310737524181</v>
       </c>
     </row>
     <row r="220">
@@ -24034,13 +23994,13 @@
         <v>4.2887</v>
       </c>
       <c r="AA220" t="n">
-        <v>1.950825229744173</v>
+        <v>1.950825229744171</v>
       </c>
       <c r="AB220" t="n">
         <v>1.417586488246888</v>
       </c>
       <c r="AC220" t="n">
-        <v>-0.3682445672670967</v>
+        <v>-0.3682445672670986</v>
       </c>
     </row>
     <row r="221">
@@ -24144,10 +24104,10 @@
         <v>-0.8074038098554324</v>
       </c>
       <c r="AB221" t="n">
-        <v>-1.030719925910027</v>
+        <v>-1.030719925910029</v>
       </c>
       <c r="AC221" t="n">
-        <v>-0.7094330331588378</v>
+        <v>-0.7094330331588367</v>
       </c>
     </row>
     <row r="222">
@@ -24248,13 +24208,13 @@
         <v>2.5276</v>
       </c>
       <c r="AA222" t="n">
-        <v>-1.685194790036501</v>
+        <v>-1.6851947900365</v>
       </c>
       <c r="AB222" t="n">
-        <v>0.5557834103003679</v>
+        <v>0.5557834103003653</v>
       </c>
       <c r="AC222" t="n">
-        <v>-1.332981589553769</v>
+        <v>-1.332981589553771</v>
       </c>
     </row>
     <row r="223">
@@ -24355,13 +24315,13 @@
         <v>3.847</v>
       </c>
       <c r="AA223" t="n">
-        <v>0.9213735931664</v>
+        <v>0.9213735931664003</v>
       </c>
       <c r="AB223" t="n">
         <v>-1.580949148038749</v>
       </c>
       <c r="AC223" t="n">
-        <v>-1.703972240675081</v>
+        <v>-1.70397224067508</v>
       </c>
     </row>
     <row r="224">
@@ -24462,13 +24422,13 @@
         <v>3.1753</v>
       </c>
       <c r="AA224" t="n">
-        <v>0.7056374551444716</v>
+        <v>0.70563745514447</v>
       </c>
       <c r="AB224" t="n">
-        <v>-0.109610178303667</v>
+        <v>-0.109610178303669</v>
       </c>
       <c r="AC224" t="n">
-        <v>-1.330141436960063</v>
+        <v>-1.330141436960065</v>
       </c>
     </row>
     <row r="225">
@@ -24569,10 +24529,10 @@
         <v>3.4377</v>
       </c>
       <c r="AA225" t="n">
-        <v>-0.7305948286068724</v>
+        <v>-0.7305948286068745</v>
       </c>
       <c r="AB225" t="n">
-        <v>1.464427149152759</v>
+        <v>1.464427149152758</v>
       </c>
       <c r="AC225" t="n">
         <v>1.256484840278506</v>
@@ -24676,13 +24636,13 @@
         <v>5.9604</v>
       </c>
       <c r="AA226" t="n">
-        <v>3.594379370511301</v>
+        <v>3.594379370511295</v>
       </c>
       <c r="AB226" t="n">
-        <v>0.2142893491985062</v>
+        <v>0.2142893491985069</v>
       </c>
       <c r="AC226" t="n">
-        <v>-0.4450004481179853</v>
+        <v>-0.4450004481179838</v>
       </c>
     </row>
     <row r="227">
@@ -24783,13 +24743,13 @@
         <v>2.6742</v>
       </c>
       <c r="AA227" t="n">
-        <v>0.545061544516531</v>
+        <v>0.5450615445165304</v>
       </c>
       <c r="AB227" t="n">
-        <v>-0.5719286432465088</v>
+        <v>-0.5719286432465095</v>
       </c>
       <c r="AC227" t="n">
-        <v>0.1726718248091085</v>
+        <v>0.1726718248091124</v>
       </c>
     </row>
     <row r="228">
@@ -24890,13 +24850,13 @@
         <v>4.0514</v>
       </c>
       <c r="AA228" t="n">
-        <v>2.526744568461957</v>
+        <v>2.526744568461956</v>
       </c>
       <c r="AB228" t="n">
-        <v>0.2717387227257111</v>
+        <v>0.2717387227257115</v>
       </c>
       <c r="AC228" t="n">
-        <v>-0.09574338684791085</v>
+        <v>-0.09574338684791198</v>
       </c>
     </row>
     <row r="229">
@@ -24997,13 +24957,13 @@
         <v>3.6956</v>
       </c>
       <c r="AA229" t="n">
-        <v>-0.5997639312400389</v>
+        <v>-0.5997639312400378</v>
       </c>
       <c r="AB229" t="n">
-        <v>0.1781374846961828</v>
+        <v>0.1781374846961847</v>
       </c>
       <c r="AC229" t="n">
-        <v>1.931199444554904</v>
+        <v>1.931199444554908</v>
       </c>
     </row>
     <row r="230">
@@ -25104,13 +25064,13 @@
         <v>3.067</v>
       </c>
       <c r="AA230" t="n">
-        <v>-0.4989293131591797</v>
+        <v>-0.4989293131591799</v>
       </c>
       <c r="AB230" t="n">
-        <v>0.5504545008245908</v>
+        <v>0.5504545008245934</v>
       </c>
       <c r="AC230" t="n">
-        <v>1.269220899895942</v>
+        <v>1.26922089989594</v>
       </c>
     </row>
     <row r="231">
@@ -25211,13 +25171,13 @@
         <v>4.3363</v>
       </c>
       <c r="AA231" t="n">
-        <v>1.483176434676648</v>
+        <v>1.483176434676645</v>
       </c>
       <c r="AB231" t="n">
-        <v>1.941150619876141</v>
+        <v>1.941150619876143</v>
       </c>
       <c r="AC231" t="n">
-        <v>0.2572386156405757</v>
+        <v>0.2572386156405723</v>
       </c>
     </row>
     <row r="232">
@@ -25318,13 +25278,13 @@
         <v>4.9155</v>
       </c>
       <c r="AA232" t="n">
-        <v>0.6544441523670663</v>
+        <v>0.6544441523670725</v>
       </c>
       <c r="AB232" t="n">
-        <v>-2.212563216628955</v>
+        <v>-2.212563216628952</v>
       </c>
       <c r="AC232" t="n">
-        <v>1.608140020603317</v>
+        <v>1.60814002060332</v>
       </c>
     </row>
     <row r="233">
@@ -25425,13 +25385,13 @@
         <v>4.0483</v>
       </c>
       <c r="AA233" t="n">
-        <v>1.394338211317272</v>
+        <v>1.394338211317271</v>
       </c>
       <c r="AB233" t="n">
-        <v>0.2757341349597669</v>
+        <v>0.2757341349597659</v>
       </c>
       <c r="AC233" t="n">
-        <v>-0.2082810821055743</v>
+        <v>-0.2082810821055732</v>
       </c>
     </row>
     <row r="234">
@@ -25532,10 +25492,10 @@
         <v>3.5351</v>
       </c>
       <c r="AA234" t="n">
-        <v>1.153764070087656</v>
+        <v>1.153764070087658</v>
       </c>
       <c r="AB234" t="n">
-        <v>-0.7049710092555743</v>
+        <v>-0.7049710092555699</v>
       </c>
       <c r="AC234" t="n">
         <v>1.08238220454874</v>
@@ -25639,13 +25599,13 @@
         <v>5.2617</v>
       </c>
       <c r="AA235" t="n">
-        <v>0.07120123334494062</v>
+        <v>0.0712012333449419</v>
       </c>
       <c r="AB235" t="n">
-        <v>2.111751449081654</v>
+        <v>2.111751449081659</v>
       </c>
       <c r="AC235" t="n">
-        <v>2.299872419735691</v>
+        <v>2.299872419735687</v>
       </c>
     </row>
     <row r="236">
@@ -25746,10 +25706,10 @@
         <v>3.3409</v>
       </c>
       <c r="AA236" t="n">
-        <v>-0.6728363871094417</v>
+        <v>-0.6728363871094386</v>
       </c>
       <c r="AB236" t="n">
-        <v>-1.09067498873493</v>
+        <v>-1.090674988734933</v>
       </c>
       <c r="AC236" t="n">
         <v>-1.354478248687584</v>
@@ -25853,13 +25813,13 @@
         <v>2.9734</v>
       </c>
       <c r="AA237" t="n">
-        <v>-0.7834896652210482</v>
+        <v>-0.783489665221049</v>
       </c>
       <c r="AB237" t="n">
-        <v>0.9069494256273325</v>
+        <v>0.9069494256273344</v>
       </c>
       <c r="AC237" t="n">
-        <v>1.488091470135027</v>
+        <v>1.488091470135028</v>
       </c>
     </row>
     <row r="238">
@@ -25960,13 +25920,13 @@
         <v>5.0383</v>
       </c>
       <c r="AA238" t="n">
-        <v>0.3200952168030375</v>
+        <v>0.3200952168030443</v>
       </c>
       <c r="AB238" t="n">
-        <v>-3.727449568584096</v>
+        <v>-3.727449568584094</v>
       </c>
       <c r="AC238" t="n">
-        <v>0.3343529623085638</v>
+        <v>0.3343529623085704</v>
       </c>
     </row>
     <row r="239">
@@ -26067,13 +26027,13 @@
         <v>2.5732</v>
       </c>
       <c r="AA239" t="n">
-        <v>-0.2227241482667301</v>
+        <v>-0.2227241482667308</v>
       </c>
       <c r="AB239" t="n">
-        <v>0.6945198678878832</v>
+        <v>0.694519867887882</v>
       </c>
       <c r="AC239" t="n">
-        <v>-1.10462539459094</v>
+        <v>-1.104625394590942</v>
       </c>
     </row>
     <row r="240">
@@ -26174,13 +26134,13 @@
         <v>3.3416</v>
       </c>
       <c r="AA240" t="n">
-        <v>0.5519027857627442</v>
+        <v>0.5519027857627459</v>
       </c>
       <c r="AB240" t="n">
-        <v>0.3647246370869967</v>
+        <v>0.3647246370869988</v>
       </c>
       <c r="AC240" t="n">
-        <v>1.045911227464043</v>
+        <v>1.045911227464044</v>
       </c>
     </row>
     <row r="241">
@@ -26281,13 +26241,13 @@
         <v>3.4902</v>
       </c>
       <c r="AA241" t="n">
-        <v>0.6218512010887342</v>
+        <v>0.621851201088737</v>
       </c>
       <c r="AB241" t="n">
-        <v>-1.580383804881723</v>
+        <v>-1.580383804881724</v>
       </c>
       <c r="AC241" t="n">
-        <v>-1.106643239986851</v>
+        <v>-1.10664323998685</v>
       </c>
     </row>
     <row r="242">
@@ -26388,13 +26348,13 @@
         <v>4.2829</v>
       </c>
       <c r="AA242" t="n">
-        <v>1.766447631603996</v>
+        <v>1.766447631603993</v>
       </c>
       <c r="AB242" t="n">
-        <v>0.7447882534232421</v>
+        <v>0.7447882534232425</v>
       </c>
       <c r="AC242" t="n">
-        <v>0.9577563660340934</v>
+        <v>0.9577563660340963</v>
       </c>
     </row>
     <row r="243">
@@ -26495,13 +26455,13 @@
         <v>3.0981</v>
       </c>
       <c r="AA243" t="n">
-        <v>0.349096554721111</v>
+        <v>0.349096554721108</v>
       </c>
       <c r="AB243" t="n">
-        <v>0.7601927607125363</v>
+        <v>0.7601927607125317</v>
       </c>
       <c r="AC243" t="n">
-        <v>-2.340808609522877</v>
+        <v>-2.34080860952288</v>
       </c>
     </row>
     <row r="244">
@@ -26602,13 +26562,13 @@
         <v>2.4149</v>
       </c>
       <c r="AA244" t="n">
-        <v>-0.8416829828232688</v>
+        <v>-0.8416829828232666</v>
       </c>
       <c r="AB244" t="n">
-        <v>0.2890115693010465</v>
+        <v>0.2890115693010469</v>
       </c>
       <c r="AC244" t="n">
-        <v>0.675901422367672</v>
+        <v>0.675901422367671</v>
       </c>
     </row>
     <row r="245">
@@ -26709,13 +26669,13 @@
         <v>3.4257</v>
       </c>
       <c r="AA245" t="n">
-        <v>0.4009938579002468</v>
+        <v>0.4009938579002494</v>
       </c>
       <c r="AB245" t="n">
-        <v>0.4270417756238941</v>
+        <v>0.4270417756238965</v>
       </c>
       <c r="AC245" t="n">
-        <v>0.9821775995121027</v>
+        <v>0.9821775995121014</v>
       </c>
     </row>
     <row r="246">
@@ -26816,13 +26776,13 @@
         <v>4.6004</v>
       </c>
       <c r="AA246" t="n">
-        <v>0.7775323144207247</v>
+        <v>0.7775323144207229</v>
       </c>
       <c r="AB246" t="n">
-        <v>1.538221458649862</v>
+        <v>1.538221458649867</v>
       </c>
       <c r="AC246" t="n">
-        <v>2.515607823051899</v>
+        <v>2.515607823051896</v>
       </c>
     </row>
     <row r="247">
@@ -26923,13 +26883,13 @@
         <v>3.2808</v>
       </c>
       <c r="AA247" t="n">
-        <v>-0.5093078977917823</v>
+        <v>-0.5093078977917825</v>
       </c>
       <c r="AB247" t="n">
         <v>1.856334976435487</v>
       </c>
       <c r="AC247" t="n">
-        <v>0.04127857735687169</v>
+        <v>0.04127857735686661</v>
       </c>
     </row>
     <row r="248">
@@ -27030,13 +26990,13 @@
         <v>4.4606</v>
       </c>
       <c r="AA248" t="n">
-        <v>0.6572625606367559</v>
+        <v>0.6572625606367599</v>
       </c>
       <c r="AB248" t="n">
-        <v>-0.9937093152520089</v>
+        <v>-0.9937093152520042</v>
       </c>
       <c r="AC248" t="n">
-        <v>2.617964767420278</v>
+        <v>2.61796476742028</v>
       </c>
     </row>
     <row r="249">
@@ -27137,13 +27097,13 @@
         <v>4.6142</v>
       </c>
       <c r="AA249" t="n">
-        <v>2.269171645720142</v>
+        <v>2.26917164572014</v>
       </c>
       <c r="AB249" t="n">
-        <v>-1.24960498882714</v>
+        <v>-1.249604988827137</v>
       </c>
       <c r="AC249" t="n">
-        <v>1.081233578527649</v>
+        <v>1.081233578527653</v>
       </c>
     </row>
     <row r="250">
@@ -27244,13 +27204,13 @@
         <v>2.7371</v>
       </c>
       <c r="AA250" t="n">
-        <v>-0.5205049315552971</v>
+        <v>-0.5205049315552976</v>
       </c>
       <c r="AB250" t="n">
-        <v>1.140531291827263</v>
+        <v>1.140531291827259</v>
       </c>
       <c r="AC250" t="n">
-        <v>-1.895004650453488</v>
+        <v>-1.895004650453491</v>
       </c>
     </row>
     <row r="251">
@@ -27351,13 +27311,13 @@
         <v>4.3327</v>
       </c>
       <c r="AA251" t="n">
-        <v>0.7597111585617224</v>
+        <v>0.7597111585617193</v>
       </c>
       <c r="AB251" t="n">
         <v>2.875130275788853</v>
       </c>
       <c r="AC251" t="n">
-        <v>-0.3367624690426486</v>
+        <v>-0.3367624690426547</v>
       </c>
     </row>
     <row r="252">
@@ -27458,13 +27418,13 @@
         <v>3.2468</v>
       </c>
       <c r="AA252" t="n">
-        <v>0.6367126382582213</v>
+        <v>0.636712638258222</v>
       </c>
       <c r="AB252" t="n">
-        <v>0.2647733684134124</v>
+        <v>0.2647733684134138</v>
       </c>
       <c r="AC252" t="n">
-        <v>0.5695685059601845</v>
+        <v>0.5695685059601833</v>
       </c>
     </row>
     <row r="253">
@@ -27565,13 +27525,13 @@
         <v>3.4822</v>
       </c>
       <c r="AA253" t="n">
-        <v>0.7653914275020277</v>
+        <v>0.7653914275020276</v>
       </c>
       <c r="AB253" t="n">
-        <v>0.5499511176389279</v>
+        <v>0.5499511176389291</v>
       </c>
       <c r="AC253" t="n">
-        <v>0.2844771127650452</v>
+        <v>0.2844771127650427</v>
       </c>
     </row>
     <row r="254">
@@ -27672,13 +27632,13 @@
         <v>3.8845</v>
       </c>
       <c r="AA254" t="n">
-        <v>1.991310350648208</v>
+        <v>1.991310350648205</v>
       </c>
       <c r="AB254" t="n">
-        <v>1.174733792904179</v>
+        <v>1.174733792904178</v>
       </c>
       <c r="AC254" t="n">
-        <v>-1.55375454196373</v>
+        <v>-1.553754541963733</v>
       </c>
     </row>
     <row r="255">
@@ -27782,10 +27742,10 @@
         <v>1.737265846654338</v>
       </c>
       <c r="AB255" t="n">
-        <v>-2.075683774573424</v>
+        <v>-2.075683774573423</v>
       </c>
       <c r="AC255" t="n">
-        <v>0.7174684831738508</v>
+        <v>0.7174684831738557</v>
       </c>
     </row>
     <row r="256">
@@ -27886,13 +27846,13 @@
         <v>3.9602</v>
       </c>
       <c r="AA256" t="n">
-        <v>0.1968183801066602</v>
+        <v>0.1968183801066573</v>
       </c>
       <c r="AB256" t="n">
-        <v>0.1353260163745175</v>
+        <v>0.1353260163745132</v>
       </c>
       <c r="AC256" t="n">
-        <v>-3.364238031940537</v>
+        <v>-3.36423803194054</v>
       </c>
     </row>
     <row r="257">
@@ -27993,13 +27953,13 @@
         <v>3.6232</v>
       </c>
       <c r="AA257" t="n">
-        <v>1.221597811264086</v>
+        <v>1.221597811264087</v>
       </c>
       <c r="AB257" t="n">
-        <v>-0.8863463726442922</v>
+        <v>-0.8863463726442884</v>
       </c>
       <c r="AC257" t="n">
-        <v>0.8771108835168532</v>
+        <v>0.8771108835168558</v>
       </c>
     </row>
     <row r="258">
@@ -28100,13 +28060,13 @@
         <v>2.7845</v>
       </c>
       <c r="AA258" t="n">
-        <v>-1.595624997133435</v>
+        <v>-1.59562499713343</v>
       </c>
       <c r="AB258" t="n">
-        <v>-0.680636762156649</v>
+        <v>-0.6806367621566498</v>
       </c>
       <c r="AC258" t="n">
-        <v>-0.3257986433322171</v>
+        <v>-0.3257986433322173</v>
       </c>
     </row>
     <row r="259">
@@ -28207,13 +28167,13 @@
         <v>2.1471</v>
       </c>
       <c r="AA259" t="n">
-        <v>-1.903646703832648</v>
+        <v>-1.903646703832645</v>
       </c>
       <c r="AB259" t="n">
-        <v>0.8975387009500234</v>
+        <v>0.8975387009500224</v>
       </c>
       <c r="AC259" t="n">
-        <v>-0.08258007238846878</v>
+        <v>-0.08258007238847039</v>
       </c>
     </row>
     <row r="260">
@@ -28314,13 +28274,13 @@
         <v>4.0709</v>
       </c>
       <c r="AA260" t="n">
-        <v>0.1787576671215053</v>
+        <v>0.1787576671215097</v>
       </c>
       <c r="AB260" t="n">
-        <v>-1.334171662797069</v>
+        <v>-1.334171662797067</v>
       </c>
       <c r="AC260" t="n">
-        <v>0.7068120909384107</v>
+        <v>0.7068120909384121</v>
       </c>
     </row>
     <row r="261">
@@ -28421,13 +28381,13 @@
         <v>5.1273</v>
       </c>
       <c r="AA261" t="n">
-        <v>2.060169137824377</v>
+        <v>2.060169137824373</v>
       </c>
       <c r="AB261" t="n">
-        <v>0.7216877896672973</v>
+        <v>0.7216877896672945</v>
       </c>
       <c r="AC261" t="n">
-        <v>-1.080721712352546</v>
+        <v>-1.080721712352543</v>
       </c>
     </row>
     <row r="262">
@@ -28528,13 +28488,13 @@
         <v>2.6895</v>
       </c>
       <c r="AA262" t="n">
-        <v>-0.1534716663594217</v>
+        <v>-0.1534716663594208</v>
       </c>
       <c r="AB262" t="n">
-        <v>-0.4877006152438143</v>
+        <v>-0.4877006152438172</v>
       </c>
       <c r="AC262" t="n">
-        <v>-1.991825878968957</v>
+        <v>-1.991825878968956</v>
       </c>
     </row>
     <row r="263">
@@ -28635,13 +28595,13 @@
         <v>3.6672</v>
       </c>
       <c r="AA263" t="n">
-        <v>-0.6651580408403126</v>
+        <v>-0.6651580408403139</v>
       </c>
       <c r="AB263" t="n">
-        <v>1.672261775622209</v>
+        <v>1.672261775622205</v>
       </c>
       <c r="AC263" t="n">
-        <v>-0.1922562093032731</v>
+        <v>-0.192256209303272</v>
       </c>
     </row>
     <row r="264">
@@ -28742,13 +28702,13 @@
         <v>3.7273</v>
       </c>
       <c r="AA264" t="n">
-        <v>0.9409743591142207</v>
+        <v>0.9409743591142198</v>
       </c>
       <c r="AB264" t="n">
         <v>2.166017458177131</v>
       </c>
       <c r="AC264" t="n">
-        <v>-0.07443800001096366</v>
+        <v>-0.07443800001096786</v>
       </c>
     </row>
     <row r="265">
@@ -28849,13 +28809,13 @@
         <v>3.3652</v>
       </c>
       <c r="AA265" t="n">
-        <v>-0.3517531345359162</v>
+        <v>-0.3517531345359144</v>
       </c>
       <c r="AB265" t="n">
-        <v>-0.7200466466545532</v>
+        <v>-0.7200466466545523</v>
       </c>
       <c r="AC265" t="n">
-        <v>0.8891324357637822</v>
+        <v>0.8891324357637881</v>
       </c>
     </row>
     <row r="266">
@@ -28956,13 +28916,13 @@
         <v>2.7538</v>
       </c>
       <c r="AA266" t="n">
-        <v>-1.705066802941673</v>
+        <v>-1.705066802941672</v>
       </c>
       <c r="AB266" t="n">
-        <v>0.7336249809042917</v>
+        <v>0.7336249809042872</v>
       </c>
       <c r="AC266" t="n">
-        <v>-1.536102388819345</v>
+        <v>-1.536102388819348</v>
       </c>
     </row>
     <row r="267">
@@ -29063,13 +29023,13 @@
         <v>2.868</v>
       </c>
       <c r="AA267" t="n">
-        <v>-2.39018203821281</v>
+        <v>-2.390182038212812</v>
       </c>
       <c r="AB267" t="n">
-        <v>-0.1205407457850156</v>
+        <v>-0.1205407457850163</v>
       </c>
       <c r="AC267" t="n">
-        <v>0.2733809260499934</v>
+        <v>0.2733809260499937</v>
       </c>
     </row>
     <row r="268">
@@ -29170,13 +29130,13 @@
         <v>2.6278</v>
       </c>
       <c r="AA268" t="n">
-        <v>-1.087212282430222</v>
+        <v>-1.087212282430223</v>
       </c>
       <c r="AB268" t="n">
         <v>-1.585572566051185</v>
       </c>
       <c r="AC268" t="n">
-        <v>-0.7442679118848667</v>
+        <v>-0.7442679118848629</v>
       </c>
     </row>
     <row r="269">
@@ -29277,13 +29237,13 @@
         <v>4.8087</v>
       </c>
       <c r="AA269" t="n">
-        <v>2.699500324927559</v>
+        <v>2.699500324927558</v>
       </c>
       <c r="AB269" t="n">
-        <v>-0.0902331169001849</v>
+        <v>-0.09023311690017957</v>
       </c>
       <c r="AC269" t="n">
-        <v>1.794779755353126</v>
+        <v>1.794779755353125</v>
       </c>
     </row>
     <row r="270">
@@ -29384,13 +29344,13 @@
         <v>2.2346</v>
       </c>
       <c r="AA270" t="n">
-        <v>-0.2414994772204445</v>
+        <v>-0.2414994772204455</v>
       </c>
       <c r="AB270" t="n">
-        <v>-0.6117374212802129</v>
+        <v>-0.6117374212802139</v>
       </c>
       <c r="AC270" t="n">
-        <v>-0.3423105147747722</v>
+        <v>-0.342310514774769</v>
       </c>
     </row>
     <row r="271">
@@ -29491,13 +29451,13 @@
         <v>3.8745</v>
       </c>
       <c r="AA271" t="n">
-        <v>1.601509947787701</v>
+        <v>1.601509947787702</v>
       </c>
       <c r="AB271" t="n">
-        <v>-1.665026803387113</v>
+        <v>-1.665026803387112</v>
       </c>
       <c r="AC271" t="n">
-        <v>-0.1410159432762268</v>
+        <v>-0.1410159432762269</v>
       </c>
     </row>
     <row r="272">
@@ -29598,13 +29558,13 @@
         <v>3.0373</v>
       </c>
       <c r="AA272" t="n">
-        <v>-0.5181601272086334</v>
+        <v>-0.5181601272086341</v>
       </c>
       <c r="AB272" t="n">
-        <v>-1.800779818424775</v>
+        <v>-1.800779818424777</v>
       </c>
       <c r="AC272" t="n">
-        <v>-1.320371254945153</v>
+        <v>-1.320371254945149</v>
       </c>
     </row>
     <row r="273">
@@ -29705,13 +29665,13 @@
         <v>3.5766</v>
       </c>
       <c r="AA273" t="n">
-        <v>0.003499381398431301</v>
+        <v>0.003499381398430186</v>
       </c>
       <c r="AB273" t="n">
-        <v>1.224015132567835</v>
+        <v>1.224015132567832</v>
       </c>
       <c r="AC273" t="n">
-        <v>-0.6944555694196421</v>
+        <v>-0.6944555694196443</v>
       </c>
     </row>
     <row r="274">
@@ -29812,13 +29772,13 @@
         <v>3.4966</v>
       </c>
       <c r="AA274" t="n">
-        <v>-0.1417288445334147</v>
+        <v>-0.1417288445334158</v>
       </c>
       <c r="AB274" t="n">
-        <v>1.099510509676969</v>
+        <v>1.099510509676966</v>
       </c>
       <c r="AC274" t="n">
-        <v>-2.030483046184776</v>
+        <v>-2.030483046184781</v>
       </c>
     </row>
     <row r="275">
@@ -29919,13 +29879,13 @@
         <v>2.8385</v>
       </c>
       <c r="AA275" t="n">
-        <v>0.0936443882629751</v>
+        <v>0.09364438826297281</v>
       </c>
       <c r="AB275" t="n">
-        <v>0.9092113493262504</v>
+        <v>0.9092113493262479</v>
       </c>
       <c r="AC275" t="n">
-        <v>-1.161784979000716</v>
+        <v>-1.161784979000721</v>
       </c>
     </row>
     <row r="276">
@@ -30026,13 +29986,13 @@
         <v>3.5332</v>
       </c>
       <c r="AA276" t="n">
-        <v>-0.5910429121973425</v>
+        <v>-0.5910429121973385</v>
       </c>
       <c r="AB276" t="n">
-        <v>-1.42675720940772</v>
+        <v>-1.426757209407718</v>
       </c>
       <c r="AC276" t="n">
-        <v>1.225605774731488</v>
+        <v>1.22560577473149</v>
       </c>
     </row>
     <row r="277">
@@ -30133,13 +30093,13 @@
         <v>3.8105</v>
       </c>
       <c r="AA277" t="n">
-        <v>-0.00234814814052846</v>
+        <v>-0.002348148140527619</v>
       </c>
       <c r="AB277" t="n">
-        <v>1.33487024375522</v>
+        <v>1.334870243755225</v>
       </c>
       <c r="AC277" t="n">
-        <v>1.984855578243504</v>
+        <v>1.984855578243501</v>
       </c>
     </row>
     <row r="278">
@@ -30240,13 +30200,13 @@
         <v>4.4796</v>
       </c>
       <c r="AA278" t="n">
-        <v>1.936986423208219</v>
+        <v>1.936986423208218</v>
       </c>
       <c r="AB278" t="n">
-        <v>1.189588521949868</v>
+        <v>1.18958852194987</v>
       </c>
       <c r="AC278" t="n">
-        <v>1.218085343770782</v>
+        <v>1.218085343770779</v>
       </c>
     </row>
     <row r="279">
@@ -30347,10 +30307,10 @@
         <v>2.3088</v>
       </c>
       <c r="AA279" t="n">
-        <v>-0.8789931891176956</v>
+        <v>-0.8789931891176974</v>
       </c>
       <c r="AB279" t="n">
-        <v>0.2899079891207646</v>
+        <v>0.2899079891207599</v>
       </c>
       <c r="AC279" t="n">
         <v>-1.463157671625361</v>
@@ -30454,13 +30414,13 @@
         <v>4.3433</v>
       </c>
       <c r="AA280" t="n">
-        <v>1.257284856748259</v>
+        <v>1.257284856748263</v>
       </c>
       <c r="AB280" t="n">
-        <v>-2.617383512111978</v>
+        <v>-2.617383512111975</v>
       </c>
       <c r="AC280" t="n">
-        <v>0.8985323493240535</v>
+        <v>0.8985323493240581</v>
       </c>
     </row>
     <row r="281">
@@ -30561,13 +30521,13 @@
         <v>3.0071</v>
       </c>
       <c r="AA281" t="n">
-        <v>-1.396371684007255</v>
+        <v>-1.396371684007254</v>
       </c>
       <c r="AB281" t="n">
-        <v>-0.2684461966182989</v>
+        <v>-0.2684461966182961</v>
       </c>
       <c r="AC281" t="n">
-        <v>1.517751998383373</v>
+        <v>1.517751998383374</v>
       </c>
     </row>
     <row r="282">
@@ -30668,13 +30628,13 @@
         <v>2.9547</v>
       </c>
       <c r="AA282" t="n">
-        <v>-0.0858631543943139</v>
+        <v>-0.08586315439431552</v>
       </c>
       <c r="AB282" t="n">
-        <v>-0.2789249648730815</v>
+        <v>-0.2789249648730838</v>
       </c>
       <c r="AC282" t="n">
-        <v>-0.522426439670076</v>
+        <v>-0.5224264396700731</v>
       </c>
     </row>
     <row r="283">
@@ -30775,13 +30735,13 @@
         <v>5.5953</v>
       </c>
       <c r="AA283" t="n">
-        <v>2.682345066610832</v>
+        <v>2.682345066610833</v>
       </c>
       <c r="AB283" t="n">
-        <v>-0.3004520196712762</v>
+        <v>-0.3004520196712807</v>
       </c>
       <c r="AC283" t="n">
-        <v>-2.396302938477554</v>
+        <v>-2.396302938477551</v>
       </c>
     </row>
     <row r="284">
@@ -30882,13 +30842,13 @@
         <v>3.4968</v>
       </c>
       <c r="AA284" t="n">
-        <v>-0.1945903494867918</v>
+        <v>-0.1945903494867902</v>
       </c>
       <c r="AB284" t="n">
         <v>1.248363992534435</v>
       </c>
       <c r="AC284" t="n">
-        <v>0.07423484583446642</v>
+        <v>0.07423484583446553</v>
       </c>
     </row>
     <row r="285">
@@ -30992,10 +30952,10 @@
         <v>1.750951474415253</v>
       </c>
       <c r="AB285" t="n">
-        <v>1.936734974028967</v>
+        <v>1.936734974028965</v>
       </c>
       <c r="AC285" t="n">
-        <v>-0.6799104310596665</v>
+        <v>-0.679910431059671</v>
       </c>
     </row>
     <row r="286">
@@ -31096,10 +31056,10 @@
         <v>3.987</v>
       </c>
       <c r="AA286" t="n">
-        <v>-0.1792418881377861</v>
+        <v>-0.1792418881377824</v>
       </c>
       <c r="AB286" t="n">
-        <v>0.1157098434254804</v>
+        <v>0.1157098434254848</v>
       </c>
       <c r="AC286" t="n">
         <v>2.19942111926054</v>
@@ -31203,13 +31163,13 @@
         <v>2.8333</v>
       </c>
       <c r="AA287" t="n">
-        <v>-2.264997124247074</v>
+        <v>-2.264997124247072</v>
       </c>
       <c r="AB287" t="n">
         <v>1.406781003228443</v>
       </c>
       <c r="AC287" t="n">
-        <v>-0.08127096861100881</v>
+        <v>-0.08127096861101309</v>
       </c>
     </row>
     <row r="288">
@@ -31310,13 +31270,13 @@
         <v>4.0634</v>
       </c>
       <c r="AA288" t="n">
-        <v>1.923876980505047</v>
+        <v>1.923876980505045</v>
       </c>
       <c r="AB288" t="n">
-        <v>-0.6678219526126444</v>
+        <v>-0.6678219526126443</v>
       </c>
       <c r="AC288" t="n">
-        <v>-1.420862115209117</v>
+        <v>-1.420862115209118</v>
       </c>
     </row>
     <row r="289">
@@ -31417,13 +31377,13 @@
         <v>2.4896</v>
       </c>
       <c r="AA289" t="n">
-        <v>0.07365386367954481</v>
+        <v>0.0736538636795443</v>
       </c>
       <c r="AB289" t="n">
-        <v>-0.3583818735774248</v>
+        <v>-0.3583818735774283</v>
       </c>
       <c r="AC289" t="n">
-        <v>-1.237450327193445</v>
+        <v>-1.237450327193443</v>
       </c>
     </row>
     <row r="290">
@@ -31524,13 +31484,13 @@
         <v>4.7296</v>
       </c>
       <c r="AA290" t="n">
-        <v>0.8090181891107859</v>
+        <v>0.8090181891107855</v>
       </c>
       <c r="AB290" t="n">
-        <v>2.094649575027632</v>
+        <v>2.094649575027634</v>
       </c>
       <c r="AC290" t="n">
-        <v>1.976809813792871</v>
+        <v>1.976809813792866</v>
       </c>
     </row>
     <row r="291">
@@ -31631,13 +31591,13 @@
         <v>3.4947</v>
       </c>
       <c r="AA291" t="n">
-        <v>-0.3510429102849913</v>
+        <v>-0.3510429102849933</v>
       </c>
       <c r="AB291" t="n">
         <v>2.589782108307049</v>
       </c>
       <c r="AC291" t="n">
-        <v>0.6376652849677141</v>
+        <v>0.6376652849677085</v>
       </c>
     </row>
     <row r="292">
@@ -31738,13 +31698,13 @@
         <v>4.6302</v>
       </c>
       <c r="AA292" t="n">
-        <v>1.514376069900892</v>
+        <v>1.514376069900891</v>
       </c>
       <c r="AB292" t="n">
-        <v>1.267952457752046</v>
+        <v>1.267952457752045</v>
       </c>
       <c r="AC292" t="n">
-        <v>-1.550546831842255</v>
+        <v>-1.55054683184226</v>
       </c>
     </row>
     <row r="293">
@@ -31845,10 +31805,10 @@
         <v>3.334</v>
       </c>
       <c r="AA293" t="n">
-        <v>0.240643576838048</v>
+        <v>0.2406435768380508</v>
       </c>
       <c r="AB293" t="n">
-        <v>-1.396787044456874</v>
+        <v>-1.396787044456872</v>
       </c>
       <c r="AC293" t="n">
         <v>1.086659042547212</v>
@@ -31952,13 +31912,13 @@
         <v>3.0618</v>
       </c>
       <c r="AA294" t="n">
-        <v>-2.153371156431318</v>
+        <v>-2.153371156431317</v>
       </c>
       <c r="AB294" t="n">
-        <v>-0.5577957165496202</v>
+        <v>-0.5577957165496216</v>
       </c>
       <c r="AC294" t="n">
-        <v>-0.4700491094628413</v>
+        <v>-0.4700491094628409</v>
       </c>
     </row>
     <row r="295">
@@ -32059,13 +32019,13 @@
         <v>4.3051</v>
       </c>
       <c r="AA295" t="n">
-        <v>1.854464003146614</v>
+        <v>1.854464003146611</v>
       </c>
       <c r="AB295" t="n">
         <v>1.720181262496769</v>
       </c>
       <c r="AC295" t="n">
-        <v>0.6150560497474592</v>
+        <v>0.6150560497474554</v>
       </c>
     </row>
     <row r="296">
@@ -32166,13 +32126,13 @@
         <v>2.3726</v>
       </c>
       <c r="AA296" t="n">
-        <v>-2.221822981026303</v>
+        <v>-2.221822981026301</v>
       </c>
       <c r="AB296" t="n">
-        <v>0.6327625562440081</v>
+        <v>0.6327625562440053</v>
       </c>
       <c r="AC296" t="n">
-        <v>-0.6913317420950212</v>
+        <v>-0.691331742095022</v>
       </c>
     </row>
     <row r="297">
@@ -32273,13 +32233,13 @@
         <v>3.6434</v>
       </c>
       <c r="AA297" t="n">
-        <v>1.146725981748744</v>
+        <v>1.146725981748745</v>
       </c>
       <c r="AB297" t="n">
-        <v>-1.645890377254989</v>
+        <v>-1.645890377254985</v>
       </c>
       <c r="AC297" t="n">
-        <v>-0.0230221694427515</v>
+        <v>-0.02302216944275173</v>
       </c>
     </row>
     <row r="298">
@@ -32380,13 +32340,13 @@
         <v>3.5743</v>
       </c>
       <c r="AA298" t="n">
-        <v>-0.9768768676828606</v>
+        <v>-0.9768768676828553</v>
       </c>
       <c r="AB298" t="n">
-        <v>-1.12134118092258</v>
+        <v>-1.121341180922579</v>
       </c>
       <c r="AC298" t="n">
-        <v>0.8637603998838216</v>
+        <v>0.8637603998838249</v>
       </c>
     </row>
     <row r="299">
@@ -32487,13 +32447,13 @@
         <v>4.8568</v>
       </c>
       <c r="AA299" t="n">
-        <v>0.7984692551498402</v>
+        <v>0.7984692551498389</v>
       </c>
       <c r="AB299" t="n">
-        <v>1.956488224545417</v>
+        <v>1.956488224545422</v>
       </c>
       <c r="AC299" t="n">
-        <v>2.381977760596042</v>
+        <v>2.381977760596039</v>
       </c>
     </row>
     <row r="300">
@@ -32594,13 +32554,13 @@
         <v>3.3933</v>
       </c>
       <c r="AA300" t="n">
-        <v>1.077585251982293</v>
+        <v>1.077585251982292</v>
       </c>
       <c r="AB300" t="n">
-        <v>-0.5887778179348589</v>
+        <v>-0.5887778179348605</v>
       </c>
       <c r="AC300" t="n">
-        <v>-0.4685104294885117</v>
+        <v>-0.468510429488508</v>
       </c>
     </row>
     <row r="301">
@@ -32701,13 +32661,13 @@
         <v>4.6109</v>
       </c>
       <c r="AA301" t="n">
-        <v>2.153368873716475</v>
+        <v>2.153368873716471</v>
       </c>
       <c r="AB301" t="n">
         <v>1.258512160423553</v>
       </c>
       <c r="AC301" t="n">
-        <v>-1.247095420450147</v>
+        <v>-1.247095420450151</v>
       </c>
     </row>
     <row r="302">
@@ -32808,13 +32768,13 @@
         <v>3.377</v>
       </c>
       <c r="AA302" t="n">
-        <v>-0.2341939349509551</v>
+        <v>-0.2341939349509586</v>
       </c>
       <c r="AB302" t="n">
-        <v>0.8132198024592819</v>
+        <v>0.8132198024592806</v>
       </c>
       <c r="AC302" t="n">
-        <v>-0.3470324563084093</v>
+        <v>-0.3470324563084092</v>
       </c>
     </row>
     <row r="303">
@@ -32915,13 +32875,13 @@
         <v>3.0088</v>
       </c>
       <c r="AA303" t="n">
-        <v>-0.4987693133111157</v>
+        <v>-0.4987693133111182</v>
       </c>
       <c r="AB303" t="n">
-        <v>0.6054903015420683</v>
+        <v>0.605490301542068</v>
       </c>
       <c r="AC303" t="n">
-        <v>-1.100052200489769</v>
+        <v>-1.100052200489776</v>
       </c>
     </row>
     <row r="304">
@@ -33022,13 +32982,13 @@
         <v>2.6566</v>
       </c>
       <c r="AA304" t="n">
-        <v>-1.433215407997375</v>
+        <v>-1.433215407997374</v>
       </c>
       <c r="AB304" t="n">
-        <v>-0.3196922890424449</v>
+        <v>-0.3196922890424464</v>
       </c>
       <c r="AC304" t="n">
-        <v>-0.8545980640961988</v>
+        <v>-0.8545980640961991</v>
       </c>
     </row>
     <row r="305">
@@ -33129,13 +33089,13 @@
         <v>2.9117</v>
       </c>
       <c r="AA305" t="n">
-        <v>-0.6562083661909449</v>
+        <v>-0.656208366190944</v>
       </c>
       <c r="AB305" t="n">
-        <v>0.103698674638553</v>
+        <v>0.103698674638552</v>
       </c>
       <c r="AC305" t="n">
-        <v>-0.1378942267513289</v>
+        <v>-0.1378942267513316</v>
       </c>
     </row>
     <row r="306">
@@ -33236,13 +33196,13 @@
         <v>2.9886</v>
       </c>
       <c r="AA306" t="n">
-        <v>-1.576045056583905</v>
+        <v>-1.576045056583904</v>
       </c>
       <c r="AB306" t="n">
-        <v>1.056631057855774</v>
+        <v>1.056631057855772</v>
       </c>
       <c r="AC306" t="n">
-        <v>-1.308260901255258</v>
+        <v>-1.308260901255261</v>
       </c>
     </row>
     <row r="307">
@@ -33343,13 +33303,13 @@
         <v>2.9163</v>
       </c>
       <c r="AA307" t="n">
-        <v>-1.493451532597308</v>
+        <v>-1.493451532597309</v>
       </c>
       <c r="AB307" t="n">
-        <v>-0.4655370714700575</v>
+        <v>-0.4655370714700619</v>
       </c>
       <c r="AC307" t="n">
-        <v>-1.056264076562307</v>
+        <v>-1.056264076562304</v>
       </c>
     </row>
     <row r="308">
@@ -33450,10 +33410,10 @@
         <v>3.0793</v>
       </c>
       <c r="AA308" t="n">
-        <v>-1.313421463658877</v>
+        <v>-1.313421463658876</v>
       </c>
       <c r="AB308" t="n">
-        <v>-0.2486381709192818</v>
+        <v>-0.2486381709192813</v>
       </c>
       <c r="AC308" t="n">
         <v>-0.4553201169694869</v>
@@ -33557,13 +33517,13 @@
         <v>4.4248</v>
       </c>
       <c r="AA309" t="n">
-        <v>1.252079940657229</v>
+        <v>1.252079940657233</v>
       </c>
       <c r="AB309" t="n">
-        <v>-2.216390217931405</v>
+        <v>-2.216390217931404</v>
       </c>
       <c r="AC309" t="n">
-        <v>-0.2604348824777783</v>
+        <v>-0.2604348824777725</v>
       </c>
     </row>
     <row r="310">
@@ -33664,13 +33624,13 @@
         <v>2.6771</v>
       </c>
       <c r="AA310" t="n">
-        <v>-0.8712102850164039</v>
+        <v>-0.8712102850164043</v>
       </c>
       <c r="AB310" t="n">
-        <v>1.691039955777404</v>
+        <v>1.691039955777403</v>
       </c>
       <c r="AC310" t="n">
-        <v>0.3624306271027601</v>
+        <v>0.3624306271027566</v>
       </c>
     </row>
     <row r="311">
@@ -33771,13 +33731,13 @@
         <v>3.2417</v>
       </c>
       <c r="AA311" t="n">
-        <v>0.6913170415505701</v>
+        <v>0.6913170415505706</v>
       </c>
       <c r="AB311" t="n">
-        <v>0.5124220386591588</v>
+        <v>0.5124220386591569</v>
       </c>
       <c r="AC311" t="n">
-        <v>-0.62378691036953</v>
+        <v>-0.6237869103695303</v>
       </c>
     </row>
     <row r="312">
@@ -33878,13 +33838,13 @@
         <v>4.4057</v>
       </c>
       <c r="AA312" t="n">
-        <v>0.9671170270692891</v>
+        <v>0.967117027069286</v>
       </c>
       <c r="AB312" t="n">
-        <v>-1.774837451853973</v>
+        <v>-1.774837451853978</v>
       </c>
       <c r="AC312" t="n">
-        <v>-3.054896797225977</v>
+        <v>-3.054896797225973</v>
       </c>
     </row>
     <row r="313">
@@ -33985,13 +33945,13 @@
         <v>2.7745</v>
       </c>
       <c r="AA313" t="n">
-        <v>0.10433894919522</v>
+        <v>0.1043389491952194</v>
       </c>
       <c r="AB313" t="n">
-        <v>-0.7375512916199248</v>
+        <v>-0.7375512916199252</v>
       </c>
       <c r="AC313" t="n">
-        <v>-0.5472837630337782</v>
+        <v>-0.5472837630337786</v>
       </c>
     </row>
     <row r="314">
@@ -34092,13 +34052,13 @@
         <v>3.3973</v>
       </c>
       <c r="AA314" t="n">
-        <v>0.3023911805049737</v>
+        <v>0.3023911805049755</v>
       </c>
       <c r="AB314" t="n">
-        <v>-0.8852757084379194</v>
+        <v>-0.8852757084379228</v>
       </c>
       <c r="AC314" t="n">
-        <v>-1.933025451452273</v>
+        <v>-1.933025451452271</v>
       </c>
     </row>
     <row r="315">
@@ -34199,13 +34159,13 @@
         <v>3.6112</v>
       </c>
       <c r="AA315" t="n">
-        <v>-0.1778116067038654</v>
+        <v>-0.1778116067038646</v>
       </c>
       <c r="AB315" t="n">
-        <v>0.6404250122442107</v>
+        <v>0.640425012244212</v>
       </c>
       <c r="AC315" t="n">
-        <v>1.087526383433581</v>
+        <v>1.08752638343358</v>
       </c>
     </row>
     <row r="316">
@@ -34309,10 +34269,10 @@
         <v>1.554803692033388</v>
       </c>
       <c r="AB316" t="n">
-        <v>-0.6883265300435708</v>
+        <v>-0.6883265300435721</v>
       </c>
       <c r="AC316" t="n">
-        <v>-0.8703594364421918</v>
+        <v>-0.8703594364421922</v>
       </c>
     </row>
     <row r="317">
@@ -34413,13 +34373,13 @@
         <v>3.4889</v>
       </c>
       <c r="AA317" t="n">
-        <v>-0.7338133369025013</v>
+        <v>-0.7338133369025009</v>
       </c>
       <c r="AB317" t="n">
-        <v>1.281829661325281</v>
+        <v>1.281829661325283</v>
       </c>
       <c r="AC317" t="n">
-        <v>1.661022377308337</v>
+        <v>1.661022377308339</v>
       </c>
     </row>
     <row r="318">
@@ -34520,13 +34480,13 @@
         <v>2.1529</v>
       </c>
       <c r="AA318" t="n">
-        <v>-1.560664268005908</v>
+        <v>-1.560664268005907</v>
       </c>
       <c r="AB318" t="n">
-        <v>-0.07582795434062102</v>
+        <v>-0.0758279543406226</v>
       </c>
       <c r="AC318" t="n">
-        <v>-0.2378925018774004</v>
+        <v>-0.237892501877398</v>
       </c>
     </row>
     <row r="319">
@@ -34627,13 +34587,13 @@
         <v>4.9569</v>
       </c>
       <c r="AA319" t="n">
-        <v>1.620631844932808</v>
+        <v>1.620631844932809</v>
       </c>
       <c r="AB319" t="n">
-        <v>-0.2759175674000239</v>
+        <v>-0.2759175674000168</v>
       </c>
       <c r="AC319" t="n">
-        <v>3.290560203323261</v>
+        <v>3.290560203323262</v>
       </c>
     </row>
     <row r="320">
@@ -34734,13 +34694,13 @@
         <v>2.5546</v>
       </c>
       <c r="AA320" t="n">
-        <v>-1.940307128948473</v>
+        <v>-1.940307128948474</v>
       </c>
       <c r="AB320" t="n">
-        <v>1.640575270489156</v>
+        <v>1.640575270489155</v>
       </c>
       <c r="AC320" t="n">
-        <v>0.2596721112315906</v>
+        <v>0.2596721112315896</v>
       </c>
     </row>
     <row r="321">
@@ -34841,13 +34801,13 @@
         <v>2.1463</v>
       </c>
       <c r="AA321" t="n">
-        <v>-0.4884267306603382</v>
+        <v>-0.4884267306603401</v>
       </c>
       <c r="AB321" t="n">
-        <v>-0.313916495640828</v>
+        <v>-0.3139164956408289</v>
       </c>
       <c r="AC321" t="n">
-        <v>-0.5591696011256632</v>
+        <v>-0.5591696011256616</v>
       </c>
     </row>
     <row r="322">
@@ -34948,13 +34908,13 @@
         <v>3.4422</v>
       </c>
       <c r="AA322" t="n">
-        <v>-1.402924817027107</v>
+        <v>-1.402924817027106</v>
       </c>
       <c r="AB322" t="n">
-        <v>0.05519913034765296</v>
+        <v>0.05519913034765665</v>
       </c>
       <c r="AC322" t="n">
-        <v>1.209983213123737</v>
+        <v>1.209983213123735</v>
       </c>
     </row>
     <row r="323">
@@ -35055,13 +35015,13 @@
         <v>3.1563</v>
       </c>
       <c r="AA323" t="n">
-        <v>-0.2974389330966861</v>
+        <v>-0.2974389330966858</v>
       </c>
       <c r="AB323" t="n">
         <v>-1.329228203874469</v>
       </c>
       <c r="AC323" t="n">
-        <v>-0.7011221092355931</v>
+        <v>-0.701122109235594</v>
       </c>
     </row>
     <row r="324">
@@ -35162,13 +35122,13 @@
         <v>4.0698</v>
       </c>
       <c r="AA324" t="n">
-        <v>0.8003207265022561</v>
+        <v>0.8003207265022595</v>
       </c>
       <c r="AB324" t="n">
         <v>-2.626272591446619</v>
       </c>
       <c r="AC324" t="n">
-        <v>-0.6995016060350668</v>
+        <v>-0.6995016060350635</v>
       </c>
     </row>
     <row r="325">
@@ -35269,13 +35229,13 @@
         <v>4.1092</v>
       </c>
       <c r="AA325" t="n">
-        <v>0.1418515384693632</v>
+        <v>0.1418515384693664</v>
       </c>
       <c r="AB325" t="n">
-        <v>-3.524163960530001</v>
+        <v>-3.524163960529999</v>
       </c>
       <c r="AC325" t="n">
-        <v>0.9286904346213344</v>
+        <v>0.9286904346213424</v>
       </c>
     </row>
     <row r="326">
@@ -35376,13 +35336,13 @@
         <v>4.2887</v>
       </c>
       <c r="AA326" t="n">
-        <v>-0.6690778369874351</v>
+        <v>-0.6690778369874339</v>
       </c>
       <c r="AB326" t="n">
-        <v>2.212209216648394</v>
+        <v>2.212209216648397</v>
       </c>
       <c r="AC326" t="n">
-        <v>1.41778915678692</v>
+        <v>1.417789156786915</v>
       </c>
     </row>
     <row r="327">
@@ -35483,13 +35443,13 @@
         <v>3.9092</v>
       </c>
       <c r="AA327" t="n">
-        <v>1.150832659352672</v>
+        <v>1.150832659352671</v>
       </c>
       <c r="AB327" t="n">
-        <v>2.20710145387305</v>
+        <v>2.207101453873048</v>
       </c>
       <c r="AC327" t="n">
-        <v>-0.5552582158088775</v>
+        <v>-0.5552582158088818</v>
       </c>
     </row>
     <row r="328">
@@ -35590,13 +35550,13 @@
         <v>3.3599</v>
       </c>
       <c r="AA328" t="n">
-        <v>0.1973550277174741</v>
+        <v>0.197355027717471</v>
       </c>
       <c r="AB328" t="n">
-        <v>1.246110195076443</v>
+        <v>1.246110195076439</v>
       </c>
       <c r="AC328" t="n">
-        <v>-0.4103807530953633</v>
+        <v>-0.4103807530953635</v>
       </c>
     </row>
     <row r="329">
@@ -35697,13 +35657,13 @@
         <v>3.1034</v>
       </c>
       <c r="AA329" t="n">
-        <v>-0.5102749259363265</v>
+        <v>-0.5102749259363263</v>
       </c>
       <c r="AB329" t="n">
-        <v>0.7047956165151804</v>
+        <v>0.7047956165151814</v>
       </c>
       <c r="AC329" t="n">
-        <v>0.7130118804979075</v>
+        <v>0.7130118804979054</v>
       </c>
     </row>
     <row r="330">
@@ -35807,10 +35767,10 @@
         <v>1.166928764323056</v>
       </c>
       <c r="AB330" t="n">
-        <v>-0.4625909930979704</v>
+        <v>-0.4625909930979706</v>
       </c>
       <c r="AC330" t="n">
-        <v>-0.8803084068212351</v>
+        <v>-0.8803084068212363</v>
       </c>
     </row>
     <row r="331">
@@ -35911,13 +35871,13 @@
         <v>4.0011</v>
       </c>
       <c r="AA331" t="n">
-        <v>1.207709144224695</v>
+        <v>1.207709144224697</v>
       </c>
       <c r="AB331" t="n">
-        <v>-2.052318095120015</v>
+        <v>-2.052318095120012</v>
       </c>
       <c r="AC331" t="n">
-        <v>0.7935361758661202</v>
+        <v>0.7935361758661214</v>
       </c>
     </row>
     <row r="332">
@@ -36018,13 +35978,13 @@
         <v>2.8535</v>
       </c>
       <c r="AA332" t="n">
-        <v>-0.3090366235308664</v>
+        <v>-0.3090366235308671</v>
       </c>
       <c r="AB332" t="n">
-        <v>-0.6289918719032643</v>
+        <v>-0.6289918719032667</v>
       </c>
       <c r="AC332" t="n">
-        <v>-1.846436348222757</v>
+        <v>-1.846436348222759</v>
       </c>
     </row>
     <row r="333">
@@ -36125,13 +36085,13 @@
         <v>3.1865</v>
       </c>
       <c r="AA333" t="n">
-        <v>0.1341798592133536</v>
+        <v>0.1341798592133508</v>
       </c>
       <c r="AB333" t="n">
-        <v>-0.5506104575303903</v>
+        <v>-0.5506104575303932</v>
       </c>
       <c r="AC333" t="n">
-        <v>-2.107350996558613</v>
+        <v>-2.107350996558615</v>
       </c>
     </row>
     <row r="334">
@@ -36232,13 +36192,13 @@
         <v>2.9431</v>
       </c>
       <c r="AA334" t="n">
-        <v>0.5080988418144998</v>
+        <v>0.5080988418144989</v>
       </c>
       <c r="AB334" t="n">
-        <v>0.4222132625476093</v>
+        <v>0.4222132625476099</v>
       </c>
       <c r="AC334" t="n">
-        <v>0.3141618075384229</v>
+        <v>0.314161807538421</v>
       </c>
     </row>
     <row r="335">
@@ -36339,13 +36299,13 @@
         <v>2.8688</v>
       </c>
       <c r="AA335" t="n">
-        <v>0.3507105389734172</v>
+        <v>0.3507105389734173</v>
       </c>
       <c r="AB335" t="n">
-        <v>0.1986611365053683</v>
+        <v>0.1986611365053657</v>
       </c>
       <c r="AC335" t="n">
-        <v>-1.827420315767481</v>
+        <v>-1.827420315767483</v>
       </c>
     </row>
     <row r="336">
@@ -36446,13 +36406,13 @@
         <v>2.2745</v>
       </c>
       <c r="AA336" t="n">
-        <v>-2.036820227583087</v>
+        <v>-2.036820227583089</v>
       </c>
       <c r="AB336" t="n">
-        <v>0.5086439126031304</v>
+        <v>0.508643912603126</v>
       </c>
       <c r="AC336" t="n">
-        <v>-1.353316821703327</v>
+        <v>-1.353316821703328</v>
       </c>
     </row>
   </sheetData>
@@ -36470,428 +36430,380 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr"/>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr"/>
+      <c r="B1" t="inlineStr">
         <is>
           <t>Frekuensi_AI</t>
         </is>
       </c>
-      <c r="C1" s="1" t="n"/>
-      <c r="D1" s="1" t="n"/>
-      <c r="E1" s="1" t="n"/>
-      <c r="F1" s="1" t="n"/>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>AI_Referensi</t>
         </is>
       </c>
-      <c r="H1" s="1" t="n"/>
-      <c r="I1" s="1" t="n"/>
-      <c r="J1" s="1" t="n"/>
-      <c r="K1" s="1" t="n"/>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>AI_Kerangka</t>
         </is>
       </c>
-      <c r="M1" s="1" t="n"/>
-      <c r="N1" s="1" t="n"/>
-      <c r="O1" s="1" t="n"/>
-      <c r="P1" s="1" t="n"/>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>AI_Grammar</t>
         </is>
       </c>
-      <c r="R1" s="1" t="n"/>
-      <c r="S1" s="1" t="n"/>
-      <c r="T1" s="1" t="n"/>
-      <c r="U1" s="1" t="n"/>
-      <c r="V1" s="1" t="inlineStr">
+      <c r="V1" t="inlineStr">
         <is>
           <t>Kualitas_Tugas</t>
         </is>
       </c>
-      <c r="W1" s="1" t="n"/>
-      <c r="X1" s="1" t="n"/>
-      <c r="Y1" s="1" t="n"/>
-      <c r="Z1" s="1" t="n"/>
-      <c r="AA1" s="1" t="inlineStr">
+      <c r="AA1" t="inlineStr">
         <is>
           <t>Efisiensi</t>
         </is>
       </c>
-      <c r="AB1" s="1" t="n"/>
-      <c r="AC1" s="1" t="n"/>
-      <c r="AD1" s="1" t="n"/>
-      <c r="AE1" s="1" t="n"/>
-      <c r="AF1" s="1" t="inlineStr">
+      <c r="AF1" t="inlineStr">
         <is>
           <t>Ketergantungan</t>
         </is>
       </c>
-      <c r="AG1" s="1" t="n"/>
-      <c r="AH1" s="1" t="n"/>
-      <c r="AI1" s="1" t="n"/>
-      <c r="AJ1" s="1" t="n"/>
-      <c r="AK1" s="1" t="inlineStr">
+      <c r="AK1" t="inlineStr">
         <is>
           <t>Reduksi_Pemahaman</t>
         </is>
       </c>
-      <c r="AL1" s="1" t="n"/>
-      <c r="AM1" s="1" t="n"/>
-      <c r="AN1" s="1" t="n"/>
-      <c r="AO1" s="1" t="n"/>
-      <c r="AP1" s="1" t="inlineStr">
+      <c r="AP1" t="inlineStr">
         <is>
           <t>Waktu_Tanpa_AI</t>
         </is>
       </c>
-      <c r="AQ1" s="1" t="n"/>
-      <c r="AR1" s="1" t="n"/>
-      <c r="AS1" s="1" t="n"/>
-      <c r="AT1" s="1" t="n"/>
-      <c r="AU1" s="1" t="inlineStr">
+      <c r="AU1" t="inlineStr">
         <is>
           <t>Waktu_Dengan_AI</t>
         </is>
       </c>
-      <c r="AV1" s="1" t="n"/>
-      <c r="AW1" s="1" t="n"/>
-      <c r="AX1" s="1" t="n"/>
-      <c r="AY1" s="1" t="n"/>
-      <c r="AZ1" s="1" t="inlineStr">
+      <c r="AZ1" t="inlineStr">
         <is>
           <t>Nilai_Sebelum_AI</t>
         </is>
       </c>
-      <c r="BA1" s="1" t="n"/>
-      <c r="BB1" s="1" t="n"/>
-      <c r="BC1" s="1" t="n"/>
-      <c r="BD1" s="1" t="n"/>
-      <c r="BE1" s="1" t="inlineStr">
+      <c r="BE1" t="inlineStr">
         <is>
           <t>Nilai_Setelah_AI</t>
         </is>
       </c>
-      <c r="BF1" s="1" t="n"/>
-      <c r="BG1" s="1" t="n"/>
-      <c r="BH1" s="1" t="n"/>
-      <c r="BI1" s="1" t="n"/>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="inlineStr"/>
-      <c r="B2" s="1" t="inlineStr">
+      <c r="A2" t="inlineStr"/>
+      <c r="B2" t="inlineStr">
         <is>
           <t>mean</t>
         </is>
       </c>
-      <c r="C2" s="1" t="inlineStr">
+      <c r="C2" t="inlineStr">
         <is>
           <t>std</t>
         </is>
       </c>
-      <c r="D2" s="1" t="inlineStr">
+      <c r="D2" t="inlineStr">
         <is>
           <t>min</t>
         </is>
       </c>
-      <c r="E2" s="1" t="inlineStr">
+      <c r="E2" t="inlineStr">
         <is>
           <t>max</t>
         </is>
       </c>
-      <c r="F2" s="1" t="inlineStr">
+      <c r="F2" t="inlineStr">
         <is>
           <t>count</t>
         </is>
       </c>
-      <c r="G2" s="1" t="inlineStr">
+      <c r="G2" t="inlineStr">
         <is>
           <t>mean</t>
         </is>
       </c>
-      <c r="H2" s="1" t="inlineStr">
+      <c r="H2" t="inlineStr">
         <is>
           <t>std</t>
         </is>
       </c>
-      <c r="I2" s="1" t="inlineStr">
+      <c r="I2" t="inlineStr">
         <is>
           <t>min</t>
         </is>
       </c>
-      <c r="J2" s="1" t="inlineStr">
+      <c r="J2" t="inlineStr">
         <is>
           <t>max</t>
         </is>
       </c>
-      <c r="K2" s="1" t="inlineStr">
+      <c r="K2" t="inlineStr">
         <is>
           <t>count</t>
         </is>
       </c>
-      <c r="L2" s="1" t="inlineStr">
+      <c r="L2" t="inlineStr">
         <is>
           <t>mean</t>
         </is>
       </c>
-      <c r="M2" s="1" t="inlineStr">
+      <c r="M2" t="inlineStr">
         <is>
           <t>std</t>
         </is>
       </c>
-      <c r="N2" s="1" t="inlineStr">
+      <c r="N2" t="inlineStr">
         <is>
           <t>min</t>
         </is>
       </c>
-      <c r="O2" s="1" t="inlineStr">
+      <c r="O2" t="inlineStr">
         <is>
           <t>max</t>
         </is>
       </c>
-      <c r="P2" s="1" t="inlineStr">
+      <c r="P2" t="inlineStr">
         <is>
           <t>count</t>
         </is>
       </c>
-      <c r="Q2" s="1" t="inlineStr">
+      <c r="Q2" t="inlineStr">
         <is>
           <t>mean</t>
         </is>
       </c>
-      <c r="R2" s="1" t="inlineStr">
+      <c r="R2" t="inlineStr">
         <is>
           <t>std</t>
         </is>
       </c>
-      <c r="S2" s="1" t="inlineStr">
+      <c r="S2" t="inlineStr">
         <is>
           <t>min</t>
         </is>
       </c>
-      <c r="T2" s="1" t="inlineStr">
+      <c r="T2" t="inlineStr">
         <is>
           <t>max</t>
         </is>
       </c>
-      <c r="U2" s="1" t="inlineStr">
+      <c r="U2" t="inlineStr">
         <is>
           <t>count</t>
         </is>
       </c>
-      <c r="V2" s="1" t="inlineStr">
+      <c r="V2" t="inlineStr">
         <is>
           <t>mean</t>
         </is>
       </c>
-      <c r="W2" s="1" t="inlineStr">
+      <c r="W2" t="inlineStr">
         <is>
           <t>std</t>
         </is>
       </c>
-      <c r="X2" s="1" t="inlineStr">
+      <c r="X2" t="inlineStr">
         <is>
           <t>min</t>
         </is>
       </c>
-      <c r="Y2" s="1" t="inlineStr">
+      <c r="Y2" t="inlineStr">
         <is>
           <t>max</t>
         </is>
       </c>
-      <c r="Z2" s="1" t="inlineStr">
+      <c r="Z2" t="inlineStr">
         <is>
           <t>count</t>
         </is>
       </c>
-      <c r="AA2" s="1" t="inlineStr">
+      <c r="AA2" t="inlineStr">
         <is>
           <t>mean</t>
         </is>
       </c>
-      <c r="AB2" s="1" t="inlineStr">
+      <c r="AB2" t="inlineStr">
         <is>
           <t>std</t>
         </is>
       </c>
-      <c r="AC2" s="1" t="inlineStr">
+      <c r="AC2" t="inlineStr">
         <is>
           <t>min</t>
         </is>
       </c>
-      <c r="AD2" s="1" t="inlineStr">
+      <c r="AD2" t="inlineStr">
         <is>
           <t>max</t>
         </is>
       </c>
-      <c r="AE2" s="1" t="inlineStr">
+      <c r="AE2" t="inlineStr">
         <is>
           <t>count</t>
         </is>
       </c>
-      <c r="AF2" s="1" t="inlineStr">
+      <c r="AF2" t="inlineStr">
         <is>
           <t>mean</t>
         </is>
       </c>
-      <c r="AG2" s="1" t="inlineStr">
+      <c r="AG2" t="inlineStr">
         <is>
           <t>std</t>
         </is>
       </c>
-      <c r="AH2" s="1" t="inlineStr">
+      <c r="AH2" t="inlineStr">
         <is>
           <t>min</t>
         </is>
       </c>
-      <c r="AI2" s="1" t="inlineStr">
+      <c r="AI2" t="inlineStr">
         <is>
           <t>max</t>
         </is>
       </c>
-      <c r="AJ2" s="1" t="inlineStr">
+      <c r="AJ2" t="inlineStr">
         <is>
           <t>count</t>
         </is>
       </c>
-      <c r="AK2" s="1" t="inlineStr">
+      <c r="AK2" t="inlineStr">
         <is>
           <t>mean</t>
         </is>
       </c>
-      <c r="AL2" s="1" t="inlineStr">
+      <c r="AL2" t="inlineStr">
         <is>
           <t>std</t>
         </is>
       </c>
-      <c r="AM2" s="1" t="inlineStr">
+      <c r="AM2" t="inlineStr">
         <is>
           <t>min</t>
         </is>
       </c>
-      <c r="AN2" s="1" t="inlineStr">
+      <c r="AN2" t="inlineStr">
         <is>
           <t>max</t>
         </is>
       </c>
-      <c r="AO2" s="1" t="inlineStr">
+      <c r="AO2" t="inlineStr">
         <is>
           <t>count</t>
         </is>
       </c>
-      <c r="AP2" s="1" t="inlineStr">
+      <c r="AP2" t="inlineStr">
         <is>
           <t>mean</t>
         </is>
       </c>
-      <c r="AQ2" s="1" t="inlineStr">
+      <c r="AQ2" t="inlineStr">
         <is>
           <t>std</t>
         </is>
       </c>
-      <c r="AR2" s="1" t="inlineStr">
+      <c r="AR2" t="inlineStr">
         <is>
           <t>min</t>
         </is>
       </c>
-      <c r="AS2" s="1" t="inlineStr">
+      <c r="AS2" t="inlineStr">
         <is>
           <t>max</t>
         </is>
       </c>
-      <c r="AT2" s="1" t="inlineStr">
+      <c r="AT2" t="inlineStr">
         <is>
           <t>count</t>
         </is>
       </c>
-      <c r="AU2" s="1" t="inlineStr">
+      <c r="AU2" t="inlineStr">
         <is>
           <t>mean</t>
         </is>
       </c>
-      <c r="AV2" s="1" t="inlineStr">
+      <c r="AV2" t="inlineStr">
         <is>
           <t>std</t>
         </is>
       </c>
-      <c r="AW2" s="1" t="inlineStr">
+      <c r="AW2" t="inlineStr">
         <is>
           <t>min</t>
         </is>
       </c>
-      <c r="AX2" s="1" t="inlineStr">
+      <c r="AX2" t="inlineStr">
         <is>
           <t>max</t>
         </is>
       </c>
-      <c r="AY2" s="1" t="inlineStr">
+      <c r="AY2" t="inlineStr">
         <is>
           <t>count</t>
         </is>
       </c>
-      <c r="AZ2" s="1" t="inlineStr">
+      <c r="AZ2" t="inlineStr">
         <is>
           <t>mean</t>
         </is>
       </c>
-      <c r="BA2" s="1" t="inlineStr">
+      <c r="BA2" t="inlineStr">
         <is>
           <t>std</t>
         </is>
       </c>
-      <c r="BB2" s="1" t="inlineStr">
+      <c r="BB2" t="inlineStr">
         <is>
           <t>min</t>
         </is>
       </c>
-      <c r="BC2" s="1" t="inlineStr">
+      <c r="BC2" t="inlineStr">
         <is>
           <t>max</t>
         </is>
       </c>
-      <c r="BD2" s="1" t="inlineStr">
+      <c r="BD2" t="inlineStr">
         <is>
           <t>count</t>
         </is>
       </c>
-      <c r="BE2" s="1" t="inlineStr">
+      <c r="BE2" t="inlineStr">
         <is>
           <t>mean</t>
         </is>
       </c>
-      <c r="BF2" s="1" t="inlineStr">
+      <c r="BF2" t="inlineStr">
         <is>
           <t>std</t>
         </is>
       </c>
-      <c r="BG2" s="1" t="inlineStr">
+      <c r="BG2" t="inlineStr">
         <is>
           <t>min</t>
         </is>
       </c>
-      <c r="BH2" s="1" t="inlineStr">
+      <c r="BH2" t="inlineStr">
         <is>
           <t>max</t>
         </is>
       </c>
-      <c r="BI2" s="1" t="inlineStr">
+      <c r="BI2" t="inlineStr">
         <is>
           <t>count</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="inlineStr">
+      <c r="A3" t="inlineStr">
         <is>
           <t>Label_Cluster</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="1" t="inlineStr">
+      <c r="A4" t="inlineStr">
         <is>
           <t>Pengguna Intensif (Beban Tugas Tinggi &amp; Penunjang Bahasa)</t>
         </is>
@@ -37078,7 +36990,7 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="1" t="inlineStr">
+      <c r="A5" t="inlineStr">
         <is>
           <t>Pengguna Kasual / Konservatif (Rendah Adopsi, Khawatir Ketergantungan)</t>
         </is>
@@ -37265,7 +37177,7 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="inlineStr">
+      <c r="A6" t="inlineStr">
         <is>
           <t>Pengguna Strategis &amp; Berprestasi Tinggi (Efisien &amp; Mandiri)</t>
         </is>
@@ -37480,22 +37392,22 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>Cluster ID</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>Kategori Klaster</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>Jumlah Mahasiswa</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>Persentase (%)</t>
         </is>
@@ -37564,210 +37476,210 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>Frekuensi_AI</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>AI_Referensi</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>AI_Kerangka</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>AI_Grammar</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>Kualitas_Tugas</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>Efisiensi</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>Ketergantungan</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>Reduksi_Pemahaman</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>Waktu_Tanpa_AI</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>Waktu_Dengan_AI</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>Nilai_Sebelum_AI</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>Nilai_Setelah_AI</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="inlineStr">
+      <c r="A2" t="inlineStr">
         <is>
           <t>PC1</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>-0.1765742808336068</v>
+        <v>-0.1765742808336076</v>
       </c>
       <c r="C2" t="n">
-        <v>-0.2606067895495041</v>
+        <v>-0.2606067895495044</v>
       </c>
       <c r="D2" t="n">
-        <v>-0.2784416649743512</v>
+        <v>-0.2784416649743507</v>
       </c>
       <c r="E2" t="n">
-        <v>0.07020533878853422</v>
+        <v>0.07020533878853311</v>
       </c>
       <c r="F2" t="n">
-        <v>0.1260078195328577</v>
+        <v>0.1260078195328572</v>
       </c>
       <c r="G2" t="n">
-        <v>0.2666270483240364</v>
+        <v>0.266627048324037</v>
       </c>
       <c r="H2" t="n">
-        <v>0.03567974445486467</v>
+        <v>0.03567974445486478</v>
       </c>
       <c r="I2" t="n">
-        <v>0.1073188468915913</v>
+        <v>0.1073188468915907</v>
       </c>
       <c r="J2" t="n">
-        <v>0.4965692290080747</v>
+        <v>0.4965692290080748</v>
       </c>
       <c r="K2" t="n">
-        <v>0.3198277324964197</v>
+        <v>0.3198277324964194</v>
       </c>
       <c r="L2" t="n">
-        <v>-0.4233340579628926</v>
+        <v>-0.4233340579628918</v>
       </c>
       <c r="M2" t="n">
         <v>-0.4365847447563541</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="inlineStr">
+      <c r="A3" t="inlineStr">
         <is>
           <t>PC2</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.4886431504713163</v>
+        <v>0.4886431504713153</v>
       </c>
       <c r="C3" t="n">
-        <v>0.3456269103624877</v>
+        <v>0.345626910362488</v>
       </c>
       <c r="D3" t="n">
-        <v>0.2684380556117838</v>
+        <v>0.2684380556117825</v>
       </c>
       <c r="E3" t="n">
-        <v>0.365931841082771</v>
+        <v>0.3659318410827705</v>
       </c>
       <c r="F3" t="n">
-        <v>0.2519776807850544</v>
+        <v>0.251977680785054</v>
       </c>
       <c r="G3" t="n">
-        <v>0.2418669063339731</v>
+        <v>0.2418669063339736</v>
       </c>
       <c r="H3" t="n">
-        <v>0.01858784116842976</v>
+        <v>0.01858784116842977</v>
       </c>
       <c r="I3" t="n">
-        <v>0.01182301469094563</v>
+        <v>0.01182301469094559</v>
       </c>
       <c r="J3" t="n">
-        <v>0.2956489577153072</v>
+        <v>0.2956489577153077</v>
       </c>
       <c r="K3" t="n">
-        <v>0.4029276099855388</v>
+        <v>0.4029276099855395</v>
       </c>
       <c r="L3" t="n">
-        <v>0.1245961918168237</v>
+        <v>0.1245961918168242</v>
       </c>
       <c r="M3" t="n">
-        <v>0.2191893900277991</v>
+        <v>0.2191893900277997</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="1" t="inlineStr">
+      <c r="A4" t="inlineStr">
         <is>
           <t>PC3</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>-0.3361355680808966</v>
+        <v>-0.3361355680808971</v>
       </c>
       <c r="C4" t="n">
-        <v>-0.1098039408792811</v>
+        <v>-0.1098039408792823</v>
       </c>
       <c r="D4" t="n">
         <v>-0.3892431949718426</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.1328031470296459</v>
+        <v>-0.1328031470296471</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.05699520511209823</v>
+        <v>-0.05699520511209917</v>
       </c>
       <c r="G4" t="n">
-        <v>-0.1128148276371024</v>
+        <v>-0.1128148276371043</v>
       </c>
       <c r="H4" t="n">
-        <v>-0.06467135364826167</v>
+        <v>-0.06467135364826157</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.03247742546837904</v>
+        <v>-0.03247742546837846</v>
       </c>
       <c r="J4" t="n">
         <v>0.3063831813421877</v>
       </c>
       <c r="K4" t="n">
-        <v>0.3612359834086784</v>
+        <v>0.3612359834086781</v>
       </c>
       <c r="L4" t="n">
-        <v>0.5035527830745039</v>
+        <v>0.503552783074504</v>
       </c>
       <c r="M4" t="n">
-        <v>0.4546083292202866</v>
+        <v>0.4546083292202863</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="1" t="inlineStr">
+      <c r="A5" t="inlineStr">
         <is>
           <t>Explained_Variance_Ratio (%)</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>16.03042546549073</v>
+        <v>16.03042546549074</v>
       </c>
       <c r="C5" t="n">
         <v>14.34342644383996</v>
       </c>
       <c r="D5" t="n">
-        <v>12.86758183265723</v>
+        <v>12.86758183265724</v>
       </c>
       <c r="E5" t="inlineStr"/>
       <c r="F5" t="inlineStr"/>
@@ -37794,27 +37706,27 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>k</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>WCSS (Inertia)</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>Silhouette Score</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>Davies-Bouldin Index</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>Calinski-Harabasz Index</t>
         </is>
